--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\5_MB MMA\09_Information\10_FTQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A808CA3E-DD4C-4955-8D1C-5ADE9948E3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56EEF4C1-FB27-406C-9DD0-4949BCBF9368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$66</definedName>
     <definedName name="DATA_01">[1]Data_Lineal!$H$4:$Y$30</definedName>
     <definedName name="DB_01">#REF!</definedName>
     <definedName name="DB_CAP01">'[2]CAPACIDAD (1)'!$X$9:$AM$29</definedName>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="59">
   <si>
     <t>*</t>
   </si>
@@ -154,6 +154,93 @@
   </si>
   <si>
     <t>Cable and Mark NG (Ventanita) Op.EOL</t>
+  </si>
+  <si>
+    <t>SCCM MMA</t>
+  </si>
+  <si>
+    <t>Falla de inspección visual en curvas sin NG Op.100</t>
+  </si>
+  <si>
+    <t>Falla por falta de caída de SAS por gravedad sin NG Op.200</t>
+  </si>
+  <si>
+    <t>Dispensado de Grasa No Uniforme en Engrane sin NG Op.200</t>
+  </si>
+  <si>
+    <t>Sensor no detecta mesa giratoria Op.400</t>
+  </si>
+  <si>
+    <t>Falla en inspección visual de Ruteo de Arnes Op.700</t>
+  </si>
+  <si>
+    <t>Falla en alimentador de Tornillos Op.800</t>
+  </si>
+  <si>
+    <t>Falla de inspección visual en Mordaza Métalica sin NG Op.100</t>
+  </si>
+  <si>
+    <t>Falla de Etiqueta por Guarda sin NG Op.300</t>
+  </si>
+  <si>
+    <t>Falla de inspección visual  Op.600</t>
+  </si>
+  <si>
+    <t>Inspección visual  no detecta PCB sin conector Op.600</t>
+  </si>
+  <si>
+    <t>Falla de inspección visual  Op.700</t>
+  </si>
+  <si>
+    <t>No pide Inspección visual  del SCAS Op.700</t>
+  </si>
+  <si>
+    <t>Mal enclipsado de Engrane en Housing (SAS) Op.200</t>
+  </si>
+  <si>
+    <t>Falla de Robot de enclipsado de Engrane en Housing (SAS) Op.200</t>
+  </si>
+  <si>
+    <t>Falla Mécanica en nido giratorio Op.500</t>
+  </si>
+  <si>
+    <t>Falla de inspección visual en Stator Housing Op.100</t>
+  </si>
+  <si>
+    <t>Falla de inspección visual en Rotor Housing Op.100</t>
+  </si>
+  <si>
+    <t>Falla de altura de cable AB Op.200</t>
+  </si>
+  <si>
+    <t>Cable Dummy dañado Op.200</t>
+  </si>
+  <si>
+    <t>Falla "Codigo de barra no corresponde a la versión"  sin NOK Op.300</t>
+  </si>
+  <si>
+    <t>Falla 3110.004 Op.EOL</t>
+  </si>
+  <si>
+    <t>Falla 2270.004 Op.EOL</t>
+  </si>
+  <si>
+    <t>Falla de inspección visual no permite colocar Bearing Ring Op.100</t>
+  </si>
+  <si>
+    <t>Falla 2110.010 Op.EOL</t>
+  </si>
+  <si>
+    <t>Falla 2230.011 Op.EOL</t>
+  </si>
+  <si>
+    <t>Falla 3310.251 Op.EOL</t>
+  </si>
+  <si>
+    <t>Falla 3121.022 Op.EOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -24258,7 +24345,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K13" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K66" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CDAA4D20-2955-41E2-BD7E-9330E166FFF4}" name="Fecha" dataDxfId="18"/>
     <tableColumn id="9" xr3:uid="{F70BB124-92DE-4024-874C-EE3BA966CDE6}" name="Semana" dataDxfId="17">
@@ -24284,7 +24371,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S18" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S66" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D688BA2E-A64E-4433-85E0-7EDBF854AF60}" name="Fecha" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{D3EA5E8D-DD68-48AC-8DAC-4A4077839479}" name="Semana" dataDxfId="5">
@@ -24563,7 +24650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A1B645-8848-474A-88BA-FA9209B01B4F}">
-  <dimension ref="A1:V830"/>
+  <dimension ref="A1:V828"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
@@ -24581,7 +24668,7 @@
     <col min="15" max="15" width="12.44140625" style="1" customWidth="1"/>
     <col min="16" max="16" width="13.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="50.44140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="56.109375" style="1" customWidth="1"/>
     <col min="19" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -24716,7 +24803,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <f t="shared" ref="J5:J13" si="0">ABS(G$3-I5)</f>
+        <f t="shared" ref="J5:J9" si="0">ABS(G$3-I5)</f>
         <v>1</v>
       </c>
       <c r="K5" s="5">
@@ -24982,7 +25069,7 @@
       <c r="B10" s="4">
         <v>46226</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -25005,7 +25092,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.12676056338028169</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="1">
         <f t="shared" ref="J10:J12" si="1">ABS(G$3-I10)</f>
         <v>0.87323943661971826</v>
       </c>
@@ -25016,7 +25103,7 @@
       <c r="M10" s="4">
         <v>46226</v>
       </c>
-      <c r="N10" s="12">
+      <c r="N10" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -25040,7 +25127,7 @@
       <c r="B11" s="4">
         <v>46226</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -25063,7 +25150,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>5.9701492537313432E-2</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="1">
         <f t="shared" si="1"/>
         <v>0.94029850746268662</v>
       </c>
@@ -25074,7 +25161,7 @@
       <c r="M11" s="4">
         <v>46226</v>
       </c>
-      <c r="N11" s="12">
+      <c r="N11" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -25098,7 +25185,7 @@
       <c r="B12" s="4">
         <v>46226</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -25115,24 +25202,24 @@
         <v>46</v>
       </c>
       <c r="H12" s="1">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="I12" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.28260869565217389</v>
-      </c>
-      <c r="J12" s="12">
+        <v>0.78260869565217395</v>
+      </c>
+      <c r="J12" s="1">
         <f t="shared" si="1"/>
-        <v>0.71739130434782616</v>
+        <v>0.21739130434782605</v>
       </c>
       <c r="K12" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.71739130434782616</v>
+        <v>0.21739130434782605</v>
       </c>
       <c r="M12" s="4">
         <v>46226</v>
       </c>
-      <c r="N12" s="12">
+      <c r="N12" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -25156,7 +25243,7 @@
       <c r="B13" s="4">
         <v>46226</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -25179,7 +25266,7 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0.2391304347826087</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="1">
         <f>ABS(G$3-I13)</f>
         <v>0.76086956521739135</v>
       </c>
@@ -25190,7 +25277,7 @@
       <c r="M13" s="4">
         <v>46226</v>
       </c>
-      <c r="N13" s="12">
+      <c r="N13" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -25211,15 +25298,44 @@
       </c>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="4"/>
-      <c r="F14" s="9"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="5"/>
+      <c r="B14" s="4">
+        <v>46230</v>
+      </c>
+      <c r="C14" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="1">
+        <v>100</v>
+      </c>
+      <c r="F14" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G14" s="1">
+        <v>46</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <f t="shared" ref="J14:J24" si="2">ABS(G$3-I14)</f>
+        <v>1</v>
+      </c>
+      <c r="K14" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
       <c r="M14" s="4">
         <v>46226</v>
       </c>
-      <c r="N14" s="12">
+      <c r="N14" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -25240,15 +25356,44 @@
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="4"/>
-      <c r="F15" s="9"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="5"/>
+      <c r="B15" s="4">
+        <v>46230</v>
+      </c>
+      <c r="C15" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="1">
+        <v>200</v>
+      </c>
+      <c r="F15" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G15" s="1">
+        <v>45</v>
+      </c>
+      <c r="H15" s="1">
+        <v>18</v>
+      </c>
+      <c r="I15" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.4</v>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" si="2"/>
+        <v>0.6</v>
+      </c>
+      <c r="K15" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.6</v>
+      </c>
       <c r="M15" s="4">
         <v>46226</v>
       </c>
-      <c r="N15" s="12">
+      <c r="N15" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -25269,15 +25414,44 @@
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B16" s="4"/>
-      <c r="F16" s="9"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="5"/>
+      <c r="B16" s="4">
+        <v>46230</v>
+      </c>
+      <c r="C16" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="1">
+        <v>300</v>
+      </c>
+      <c r="F16" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G16" s="1">
+        <v>45</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K16" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
       <c r="M16" s="4">
         <v>46226</v>
       </c>
-      <c r="N16" s="12">
+      <c r="N16" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -25298,15 +25472,44 @@
       </c>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B17" s="4"/>
-      <c r="F17" s="9"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="5"/>
+      <c r="B17" s="4">
+        <v>46230</v>
+      </c>
+      <c r="C17" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="1">
+        <v>400</v>
+      </c>
+      <c r="F17" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G17" s="1">
+        <v>45</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K17" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
       <c r="M17" s="4">
         <v>46226</v>
       </c>
-      <c r="N17" s="12">
+      <c r="N17" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -25327,15 +25530,44 @@
       </c>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B18" s="4"/>
-      <c r="F18" s="9"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="5"/>
+      <c r="B18" s="4">
+        <v>46230</v>
+      </c>
+      <c r="C18" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="1">
+        <v>500</v>
+      </c>
+      <c r="F18" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G18" s="1">
+        <v>13</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K18" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
       <c r="M18" s="4">
         <v>46226</v>
       </c>
-      <c r="N18" s="12">
+      <c r="N18" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
         <v>30</v>
       </c>
@@ -25356,521 +25588,2886 @@
       </c>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B19" s="4"/>
-      <c r="F19" s="9"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="5"/>
-      <c r="M19" s="4"/>
-      <c r="Q19" s="9"/>
+      <c r="B19" s="4">
+        <v>46230</v>
+      </c>
+      <c r="C19" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="1">
+        <v>600</v>
+      </c>
+      <c r="F19" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G19" s="1">
+        <v>9</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K19" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M19" s="4">
+        <v>46230</v>
+      </c>
+      <c r="N19" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P19" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q19" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S19" s="1">
+        <v>230</v>
+      </c>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B20" s="4"/>
-      <c r="F20" s="9"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="5"/>
-      <c r="M20" s="4"/>
-      <c r="Q20" s="9"/>
+      <c r="B20" s="4">
+        <v>46231</v>
+      </c>
+      <c r="C20" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="1">
+        <v>100</v>
+      </c>
+      <c r="F20" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G20" s="1">
+        <v>9</v>
+      </c>
+      <c r="H20" s="1">
+        <v>2</v>
+      </c>
+      <c r="I20" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="J20" s="1">
+        <f t="shared" si="2"/>
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="K20" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="M20" s="4">
+        <v>46230</v>
+      </c>
+      <c r="N20" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P20" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q20" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="S20" s="1">
+        <v>6</v>
+      </c>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B21" s="4"/>
-      <c r="F21" s="9"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="5"/>
-      <c r="M21" s="4"/>
-      <c r="Q21" s="9"/>
+      <c r="B21" s="4">
+        <v>46231</v>
+      </c>
+      <c r="C21" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="1">
+        <v>200</v>
+      </c>
+      <c r="F21" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G21" s="1">
+        <v>9</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K21" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M21" s="4">
+        <v>46230</v>
+      </c>
+      <c r="N21" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P21" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q21" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="S21" s="1">
+        <v>12</v>
+      </c>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B22" s="4"/>
-      <c r="F22" s="9"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="5"/>
-      <c r="M22" s="4"/>
-      <c r="Q22" s="9"/>
+      <c r="B22" s="4">
+        <v>46231</v>
+      </c>
+      <c r="C22" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="1">
+        <v>300</v>
+      </c>
+      <c r="F22" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G22" s="1">
+        <v>46</v>
+      </c>
+      <c r="H22" s="1">
+        <v>13</v>
+      </c>
+      <c r="I22" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.28260869565217389</v>
+      </c>
+      <c r="J22" s="1">
+        <f t="shared" si="2"/>
+        <v>0.71739130434782616</v>
+      </c>
+      <c r="K22" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.71739130434782616</v>
+      </c>
+      <c r="M22" s="4">
+        <v>46231</v>
+      </c>
+      <c r="N22" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P22" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S22" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B23" s="4"/>
-      <c r="F23" s="9"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="5"/>
-      <c r="M23" s="4"/>
-      <c r="Q23" s="9"/>
+      <c r="B23" s="4">
+        <v>46231</v>
+      </c>
+      <c r="C23" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="1">
+        <v>400</v>
+      </c>
+      <c r="F23" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G23" s="1">
+        <v>9</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K23" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M23" s="4">
+        <v>46231</v>
+      </c>
+      <c r="N23" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P23" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q23" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S23" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B24" s="4"/>
-      <c r="F24" s="9"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="5"/>
-      <c r="M24" s="4"/>
-      <c r="Q24" s="9"/>
+      <c r="B24" s="4">
+        <v>46231</v>
+      </c>
+      <c r="C24" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="1">
+        <v>500</v>
+      </c>
+      <c r="F24" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G24" s="1">
+        <v>16</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K24" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M24" s="4">
+        <v>46231</v>
+      </c>
+      <c r="N24" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P24" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q24" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S24" s="1">
+        <v>6</v>
+      </c>
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B25" s="4"/>
-      <c r="F25" s="9"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="5"/>
-      <c r="M25" s="4"/>
-      <c r="Q25" s="9"/>
+      <c r="B25" s="4">
+        <v>46231</v>
+      </c>
+      <c r="C25" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="1">
+        <v>600</v>
+      </c>
+      <c r="F25" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G25" s="1">
+        <v>39</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <f t="shared" ref="J25:J32" si="3">ABS(G$3-I25)</f>
+        <v>1</v>
+      </c>
+      <c r="K25" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M25" s="4">
+        <v>46231</v>
+      </c>
+      <c r="N25" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P25" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q25" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S25" s="1">
+        <v>45</v>
+      </c>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B26" s="4"/>
-      <c r="F26" s="9"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="5"/>
-      <c r="M26" s="4"/>
-      <c r="Q26" s="9"/>
+      <c r="B26" s="4">
+        <v>46231</v>
+      </c>
+      <c r="C26" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="1">
+        <v>700</v>
+      </c>
+      <c r="F26" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G26" s="1">
+        <v>45</v>
+      </c>
+      <c r="H26" s="1">
+        <v>35</v>
+      </c>
+      <c r="I26" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="J26" s="1">
+        <f t="shared" si="3"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="K26" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="M26" s="4">
+        <v>46231</v>
+      </c>
+      <c r="N26" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P26" s="1">
+        <v>800</v>
+      </c>
+      <c r="Q26" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S26" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B27" s="4"/>
-      <c r="F27" s="9"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="5"/>
-      <c r="M27" s="4"/>
-      <c r="Q27" s="9"/>
+      <c r="B27" s="4">
+        <v>46231</v>
+      </c>
+      <c r="C27" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="1">
+        <v>800</v>
+      </c>
+      <c r="F27" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G27" s="1">
+        <v>45</v>
+      </c>
+      <c r="H27" s="1">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="J27" s="1">
+        <f t="shared" si="3"/>
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="K27" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="M27" s="4">
+        <v>46234</v>
+      </c>
+      <c r="N27" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P27" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q27" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S27" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B28" s="4"/>
-      <c r="F28" s="9"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="5"/>
-      <c r="M28" s="4"/>
-      <c r="Q28" s="9"/>
+      <c r="B28" s="4">
+        <v>46234</v>
+      </c>
+      <c r="C28" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="1">
+        <v>100</v>
+      </c>
+      <c r="F28" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="G28" s="1">
+        <v>101</v>
+      </c>
+      <c r="H28" s="1">
+        <v>8</v>
+      </c>
+      <c r="I28" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>7.9207920792079209E-2</v>
+      </c>
+      <c r="J28" s="1">
+        <f t="shared" si="3"/>
+        <v>0.92079207920792083</v>
+      </c>
+      <c r="K28" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.92079207920792083</v>
+      </c>
+      <c r="M28" s="4">
+        <v>46234</v>
+      </c>
+      <c r="N28" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P28" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q28" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S28" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B29" s="4"/>
-      <c r="F29" s="9"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="5"/>
-      <c r="M29" s="4"/>
-      <c r="Q29" s="9"/>
+      <c r="B29" s="4">
+        <v>46234</v>
+      </c>
+      <c r="C29" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="1">
+        <v>200</v>
+      </c>
+      <c r="F29" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="G29" s="1">
+        <v>100</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="1">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="K29" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M29" s="4">
+        <v>46234</v>
+      </c>
+      <c r="N29" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P29" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q29" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S29" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B30" s="4"/>
-      <c r="F30" s="9"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="5"/>
-      <c r="M30" s="4"/>
-      <c r="Q30" s="9"/>
+      <c r="B30" s="4">
+        <v>46234</v>
+      </c>
+      <c r="C30" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="1">
+        <v>300</v>
+      </c>
+      <c r="F30" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="G30" s="1">
+        <v>100</v>
+      </c>
+      <c r="H30" s="1">
+        <v>3</v>
+      </c>
+      <c r="I30" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.03</v>
+      </c>
+      <c r="J30" s="1">
+        <f t="shared" si="3"/>
+        <v>0.97</v>
+      </c>
+      <c r="K30" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.97</v>
+      </c>
+      <c r="M30" s="4">
+        <v>46234</v>
+      </c>
+      <c r="N30" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P30" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q30" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S30" s="1">
+        <v>22</v>
+      </c>
     </row>
     <row r="31" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B31" s="4"/>
-      <c r="F31" s="9"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="5"/>
-      <c r="M31" s="4"/>
-      <c r="Q31" s="9"/>
+      <c r="B31" s="4">
+        <v>46234</v>
+      </c>
+      <c r="C31" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="1">
+        <v>400</v>
+      </c>
+      <c r="F31" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="G31" s="1">
+        <v>116</v>
+      </c>
+      <c r="H31" s="1">
+        <v>22</v>
+      </c>
+      <c r="I31" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.18965517241379309</v>
+      </c>
+      <c r="J31" s="1">
+        <f t="shared" si="3"/>
+        <v>0.81034482758620685</v>
+      </c>
+      <c r="K31" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.81034482758620685</v>
+      </c>
+      <c r="M31" s="4">
+        <v>46234</v>
+      </c>
+      <c r="N31" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P31" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q31" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S31" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="32" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B32" s="4"/>
-      <c r="F32" s="9"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="5"/>
-      <c r="M32" s="4"/>
-      <c r="Q32" s="9"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B33" s="4"/>
-      <c r="F33" s="9"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="5"/>
-      <c r="M33" s="4"/>
-      <c r="Q33" s="9"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B34" s="4"/>
-      <c r="F34" s="9"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="5"/>
-      <c r="M34" s="4"/>
-      <c r="Q34" s="9"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B35" s="4"/>
-      <c r="F35" s="9"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="5"/>
-      <c r="M35" s="4"/>
-      <c r="Q35" s="9"/>
-    </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B36" s="4"/>
-      <c r="F36" s="9"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="5"/>
-      <c r="M36" s="4"/>
-      <c r="Q36" s="9"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B37" s="4"/>
-      <c r="F37" s="9"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="5"/>
-      <c r="M37" s="4"/>
-      <c r="Q37" s="9"/>
-    </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B38" s="4"/>
-      <c r="F38" s="9"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="5"/>
-      <c r="M38" s="4"/>
-      <c r="Q38" s="9"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B39" s="4"/>
-      <c r="F39" s="9"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="5"/>
-      <c r="M39" s="4"/>
-      <c r="Q39" s="9"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B40" s="4"/>
-      <c r="F40" s="9"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="5"/>
-      <c r="M40" s="4"/>
-      <c r="Q40" s="9"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B41" s="4"/>
-      <c r="F41" s="9"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="5"/>
-      <c r="M41" s="4"/>
-      <c r="Q41" s="9"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B42" s="4"/>
-      <c r="F42" s="9"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="5"/>
-      <c r="M42" s="4"/>
-      <c r="Q42" s="9"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B43" s="4"/>
-      <c r="F43" s="9"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="5"/>
-      <c r="M43" s="4"/>
-      <c r="Q43" s="9"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B44" s="4"/>
-      <c r="F44" s="9"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="5"/>
-      <c r="M44" s="4"/>
-      <c r="Q44" s="9"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B45" s="4"/>
-      <c r="F45" s="9"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="5"/>
-      <c r="M45" s="4"/>
-      <c r="Q45" s="9"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B46" s="4"/>
-      <c r="F46" s="9"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="5"/>
-      <c r="M46" s="4"/>
-      <c r="Q46" s="9"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B47" s="4"/>
-      <c r="F47" s="9"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="5"/>
-      <c r="M47" s="4"/>
-      <c r="Q47" s="9"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B48" s="4"/>
-      <c r="F48" s="9"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="5"/>
-      <c r="M48" s="4"/>
-      <c r="Q48" s="9"/>
-    </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B49" s="4"/>
-      <c r="F49" s="9"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="5"/>
-      <c r="M49" s="4"/>
-      <c r="Q49" s="9"/>
-    </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B50" s="4"/>
-      <c r="F50" s="9"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="5"/>
-      <c r="M50" s="4"/>
-      <c r="Q50" s="9"/>
-    </row>
-    <row r="51" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B51" s="4"/>
-      <c r="F51" s="9"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="5"/>
-      <c r="M51" s="4"/>
-      <c r="Q51" s="9"/>
-    </row>
-    <row r="52" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B52" s="4"/>
-      <c r="F52" s="9"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="5"/>
-      <c r="M52" s="4"/>
-      <c r="Q52" s="9"/>
-    </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B53" s="4"/>
-      <c r="F53" s="9"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="5"/>
-      <c r="M53" s="4"/>
-      <c r="Q53" s="9"/>
-    </row>
-    <row r="54" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B54" s="4"/>
-      <c r="F54" s="9"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="5"/>
-      <c r="M54" s="4"/>
-      <c r="Q54" s="9"/>
-    </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B55" s="4"/>
-      <c r="F55" s="9"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="5"/>
-      <c r="M55" s="4"/>
-      <c r="Q55" s="9"/>
-    </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B56" s="4"/>
-      <c r="F56" s="9"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="5"/>
-      <c r="M56" s="4"/>
-      <c r="Q56" s="9"/>
-    </row>
-    <row r="57" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B57" s="4"/>
-      <c r="F57" s="9"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="5"/>
-      <c r="M57" s="4"/>
-      <c r="Q57" s="9"/>
-    </row>
-    <row r="58" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B58" s="4"/>
-      <c r="F58" s="9"/>
-      <c r="I58" s="3"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="5"/>
-      <c r="M58" s="4"/>
-      <c r="Q58" s="9"/>
-    </row>
-    <row r="59" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B59" s="4"/>
-      <c r="F59" s="9"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="5"/>
-      <c r="M59" s="4"/>
-      <c r="Q59" s="9"/>
-    </row>
-    <row r="60" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B60" s="4"/>
-      <c r="F60" s="9"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="5"/>
-      <c r="M60" s="4"/>
-      <c r="Q60" s="9"/>
-    </row>
-    <row r="61" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B61" s="4"/>
-      <c r="F61" s="9"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="5"/>
-      <c r="M61" s="4"/>
-      <c r="Q61" s="9"/>
-    </row>
-    <row r="62" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B62" s="4"/>
-      <c r="F62" s="9"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="5"/>
-      <c r="M62" s="4"/>
-    </row>
-    <row r="63" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B63" s="4"/>
-      <c r="I63" s="3"/>
-      <c r="J63" s="1"/>
-      <c r="K63" s="5"/>
-      <c r="M63" s="4"/>
-    </row>
-    <row r="64" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B64" s="4"/>
-      <c r="I64" s="3"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="5"/>
-      <c r="M64" s="4"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B65" s="4"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="1"/>
-      <c r="K65" s="5"/>
-      <c r="M65" s="4"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B66" s="4"/>
-      <c r="I66" s="3"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="5"/>
-      <c r="M66" s="4"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B32" s="4">
+        <v>46234</v>
+      </c>
+      <c r="C32" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="1">
+        <v>500</v>
+      </c>
+      <c r="F32" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="G32" s="1">
+        <v>94</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="K32" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M32" s="4">
+        <v>46234</v>
+      </c>
+      <c r="N32" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P32" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q32" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S32" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B33" s="4">
+        <v>46234</v>
+      </c>
+      <c r="C33" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="1">
+        <v>600</v>
+      </c>
+      <c r="F33" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="G33" s="1">
+        <v>94</v>
+      </c>
+      <c r="H33" s="1">
+        <v>5</v>
+      </c>
+      <c r="I33" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>5.3191489361702128E-2</v>
+      </c>
+      <c r="J33" s="1">
+        <f t="shared" ref="J33:J37" si="4">ABS(G$3-I33)</f>
+        <v>0.94680851063829785</v>
+      </c>
+      <c r="K33" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.94680851063829785</v>
+      </c>
+      <c r="M33" s="4">
+        <v>46234</v>
+      </c>
+      <c r="N33" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P33" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q33" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S33" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B34" s="4">
+        <v>46234</v>
+      </c>
+      <c r="C34" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="1">
+        <v>700</v>
+      </c>
+      <c r="F34" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="G34" s="1">
+        <v>94</v>
+      </c>
+      <c r="H34" s="1">
+        <v>4</v>
+      </c>
+      <c r="I34" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>4.2553191489361701E-2</v>
+      </c>
+      <c r="J34" s="1">
+        <f t="shared" si="4"/>
+        <v>0.95744680851063835</v>
+      </c>
+      <c r="K34" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.95744680851063835</v>
+      </c>
+      <c r="M34" s="4">
+        <v>46234</v>
+      </c>
+      <c r="N34" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P34" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q34" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S34" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B35" s="4">
+        <v>46234</v>
+      </c>
+      <c r="C35" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="1">
+        <v>800</v>
+      </c>
+      <c r="F35" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="G35" s="1">
+        <v>94</v>
+      </c>
+      <c r="H35" s="10">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K35" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M35" s="4">
+        <v>46238</v>
+      </c>
+      <c r="N35" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P35" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q35" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="S35" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B36" s="4">
+        <v>46238</v>
+      </c>
+      <c r="C36" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="1">
+        <v>100</v>
+      </c>
+      <c r="F36" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="G36" s="1">
+        <v>13</v>
+      </c>
+      <c r="H36" s="1">
+        <v>11</v>
+      </c>
+      <c r="I36" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="J36" s="1">
+        <f t="shared" si="4"/>
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="K36" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="M36" s="4">
+        <v>46238</v>
+      </c>
+      <c r="N36" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P36" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q36" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S36" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B37" s="4">
+        <v>46238</v>
+      </c>
+      <c r="C37" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="1">
+        <v>200</v>
+      </c>
+      <c r="F37" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="G37" s="1">
+        <v>13</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K37" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M37" s="4">
+        <v>46238</v>
+      </c>
+      <c r="N37" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P37" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q37" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S37" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B38" s="4">
+        <v>46238</v>
+      </c>
+      <c r="C38" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="1">
+        <v>300</v>
+      </c>
+      <c r="F38" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="G38" s="1">
+        <v>13</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="1">
+        <f t="shared" ref="J38:J45" si="5">ABS(G$3-I38)</f>
+        <v>1</v>
+      </c>
+      <c r="K38" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M38" s="4">
+        <v>46238</v>
+      </c>
+      <c r="N38" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P38" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q38" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S38" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B39" s="4">
+        <v>46238</v>
+      </c>
+      <c r="C39" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" s="1">
+        <v>400</v>
+      </c>
+      <c r="F39" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="G39" s="1">
+        <v>13</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K39" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M39" s="4">
+        <v>46238</v>
+      </c>
+      <c r="N39" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P39" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q39" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S39" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B40" s="4">
+        <v>46238</v>
+      </c>
+      <c r="C40" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" s="1">
+        <v>500</v>
+      </c>
+      <c r="F40" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="G40" s="1">
+        <v>13</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K40" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M40" s="4">
+        <v>46238</v>
+      </c>
+      <c r="N40" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P40" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q40" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S40" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B41" s="4">
+        <v>46238</v>
+      </c>
+      <c r="C41" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E41" s="1">
+        <v>600</v>
+      </c>
+      <c r="F41" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="G41" s="1">
+        <v>13</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K41" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M41" s="4">
+        <v>46238</v>
+      </c>
+      <c r="N41" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P41" s="1">
+        <v>500</v>
+      </c>
+      <c r="Q41" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="R41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S41" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B42" s="4">
+        <v>46238</v>
+      </c>
+      <c r="C42" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E42" s="1">
+        <v>700</v>
+      </c>
+      <c r="F42" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="G42" s="1">
+        <v>13</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K42" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M42" s="4">
+        <v>46232</v>
+      </c>
+      <c r="N42" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P42" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q42" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S42" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B43" s="4">
+        <v>46238</v>
+      </c>
+      <c r="C43" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E43" s="1">
+        <v>800</v>
+      </c>
+      <c r="F43" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="G43" s="1">
+        <v>13</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K43" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M43" s="4">
+        <v>46232</v>
+      </c>
+      <c r="N43" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P43" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q43" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S43" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B44" s="4">
+        <v>46238</v>
+      </c>
+      <c r="C44" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E44" s="1">
+        <v>100</v>
+      </c>
+      <c r="F44" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G44" s="1">
+        <v>42</v>
+      </c>
+      <c r="H44" s="1">
+        <v>21</v>
+      </c>
+      <c r="I44" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.5</v>
+      </c>
+      <c r="J44" s="1">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="K44" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.5</v>
+      </c>
+      <c r="M44" s="4">
+        <v>46232</v>
+      </c>
+      <c r="N44" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P44" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q44" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S44" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B45" s="4">
+        <v>46238</v>
+      </c>
+      <c r="C45" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E45" s="1">
+        <v>200</v>
+      </c>
+      <c r="F45" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G45" s="1">
+        <v>42</v>
+      </c>
+      <c r="H45" s="1">
+        <v>9</v>
+      </c>
+      <c r="I45" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="J45" s="1">
+        <f t="shared" si="5"/>
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="K45" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="M45" s="4">
+        <v>46232</v>
+      </c>
+      <c r="N45" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P45" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q45" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S45" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B46" s="4">
+        <v>46238</v>
+      </c>
+      <c r="C46" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E46" s="1">
+        <v>300</v>
+      </c>
+      <c r="F46" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G46" s="1">
+        <v>42</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="1">
+        <f t="shared" ref="J46:J51" si="6">ABS(G$3-I46)</f>
+        <v>1</v>
+      </c>
+      <c r="K46" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M46" s="4">
+        <v>46232</v>
+      </c>
+      <c r="N46" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P46" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q46" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R46" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B47" s="4">
+        <v>46238</v>
+      </c>
+      <c r="C47" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E47" s="1">
+        <v>400</v>
+      </c>
+      <c r="F47" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G47" s="1">
+        <v>42</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="K47" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M47" s="4">
+        <v>46232</v>
+      </c>
+      <c r="N47" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P47" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q47" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R47" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S47" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B48" s="4">
+        <v>46238</v>
+      </c>
+      <c r="C48" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E48" s="1">
+        <v>500</v>
+      </c>
+      <c r="F48" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G48" s="1">
+        <v>42</v>
+      </c>
+      <c r="H48" s="1">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.11904761904761904</v>
+      </c>
+      <c r="J48" s="1">
+        <f t="shared" si="6"/>
+        <v>0.88095238095238093</v>
+      </c>
+      <c r="K48" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.88095238095238093</v>
+      </c>
+      <c r="M48" s="4">
+        <v>46232</v>
+      </c>
+      <c r="N48" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q48" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R48" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S48" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B49" s="4">
+        <v>46238</v>
+      </c>
+      <c r="C49" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E49" s="1">
+        <v>600</v>
+      </c>
+      <c r="F49" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G49" s="1">
+        <v>42</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="K49" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M49" s="4">
+        <v>46232</v>
+      </c>
+      <c r="N49" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q49" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R49" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S49" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B50" s="4">
+        <v>46238</v>
+      </c>
+      <c r="C50" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E50" s="1">
+        <v>700</v>
+      </c>
+      <c r="F50" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G50" s="1">
+        <v>42</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="K50" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M50" s="4">
+        <v>46232</v>
+      </c>
+      <c r="N50" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q50" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R50" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S50" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B51" s="4">
+        <v>46238</v>
+      </c>
+      <c r="C51" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E51" s="1">
+        <v>800</v>
+      </c>
+      <c r="F51" s="9">
+        <v>12289497</v>
+      </c>
+      <c r="G51" s="1">
+        <v>42</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="K51" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M51" s="4">
+        <v>46232</v>
+      </c>
+      <c r="N51" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q51" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S51" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B52" s="4">
+        <v>46232</v>
+      </c>
+      <c r="C52" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" s="1">
+        <v>100</v>
+      </c>
+      <c r="F52" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G52" s="1">
+        <v>120</v>
+      </c>
+      <c r="H52" s="1">
+        <v>31</v>
+      </c>
+      <c r="I52" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.25833333333333336</v>
+      </c>
+      <c r="J52" s="12">
+        <f t="shared" ref="J52:J60" si="7">ABS(G$3-I52)</f>
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="K52" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="M52" s="4">
+        <v>46239</v>
+      </c>
+      <c r="N52" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P52" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q52" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R52" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="S52" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B53" s="4">
+        <v>46232</v>
+      </c>
+      <c r="C53" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="1">
+        <v>150</v>
+      </c>
+      <c r="F53" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G53" s="1">
+        <v>105</v>
+      </c>
+      <c r="H53" s="1">
+        <v>9</v>
+      </c>
+      <c r="I53" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>8.5714285714285715E-2</v>
+      </c>
+      <c r="J53" s="12">
+        <f t="shared" si="7"/>
+        <v>0.91428571428571426</v>
+      </c>
+      <c r="K53" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.91428571428571426</v>
+      </c>
+      <c r="M53" s="4">
+        <v>46239</v>
+      </c>
+      <c r="N53" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P53" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q53" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R53" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S53" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B54" s="4">
+        <v>46232</v>
+      </c>
+      <c r="C54" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" s="1">
+        <v>200</v>
+      </c>
+      <c r="F54" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G54" s="1">
+        <v>105</v>
+      </c>
+      <c r="H54" s="1">
+        <v>16</v>
+      </c>
+      <c r="I54" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.15238095238095239</v>
+      </c>
+      <c r="J54" s="12">
+        <f t="shared" si="7"/>
+        <v>0.84761904761904761</v>
+      </c>
+      <c r="K54" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.84761904761904761</v>
+      </c>
+      <c r="M54" s="4">
+        <v>46239</v>
+      </c>
+      <c r="N54" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P54" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q54" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S54" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B55" s="4">
+        <v>46232</v>
+      </c>
+      <c r="C55" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" s="1">
+        <v>300</v>
+      </c>
+      <c r="F55" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G55" s="1">
+        <v>101</v>
+      </c>
+      <c r="H55" s="1">
+        <v>6</v>
+      </c>
+      <c r="I55" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>5.9405940594059403E-2</v>
+      </c>
+      <c r="J55" s="12">
+        <f t="shared" si="7"/>
+        <v>0.94059405940594054</v>
+      </c>
+      <c r="K55" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.94059405940594054</v>
+      </c>
+      <c r="M55" s="4">
+        <v>46237</v>
+      </c>
+      <c r="N55" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P55" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q55" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R55" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S55" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B56" s="4">
+        <v>46232</v>
+      </c>
+      <c r="C56" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F56" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G56" s="1">
+        <v>58</v>
+      </c>
+      <c r="H56" s="1">
+        <v>41</v>
+      </c>
+      <c r="I56" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.7068965517241379</v>
+      </c>
+      <c r="J56" s="12">
+        <f t="shared" si="7"/>
+        <v>0.2931034482758621</v>
+      </c>
+      <c r="K56" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.2931034482758621</v>
+      </c>
+      <c r="M56" s="4">
+        <v>46239</v>
+      </c>
+      <c r="N56" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P56" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q56" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R56" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S56" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B57" s="4">
+        <v>46237</v>
+      </c>
+      <c r="C57" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E57" s="1">
+        <v>100</v>
+      </c>
+      <c r="F57" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G57" s="1">
+        <v>174</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J57" s="12">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K57" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M57" s="4">
+        <v>46239</v>
+      </c>
+      <c r="N57" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P57" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q57" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R57" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S57" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B58" s="4">
+        <v>46237</v>
+      </c>
+      <c r="C58" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" s="1">
+        <v>150</v>
+      </c>
+      <c r="F58" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G58" s="1">
+        <v>174</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J58" s="12">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K58" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M58" s="4">
+        <v>46237</v>
+      </c>
+      <c r="N58" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q58" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R58" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S58" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B59" s="4">
+        <v>46237</v>
+      </c>
+      <c r="C59" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59" s="1">
+        <v>200</v>
+      </c>
+      <c r="F59" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G59" s="1">
+        <v>174</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J59" s="12">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K59" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M59" s="4">
+        <v>46237</v>
+      </c>
+      <c r="N59" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q59" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R59" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S59" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B60" s="4">
+        <v>46237</v>
+      </c>
+      <c r="C60" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" s="1">
+        <v>300</v>
+      </c>
+      <c r="F60" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G60" s="1">
+        <v>174</v>
+      </c>
+      <c r="H60" s="1">
+        <v>6</v>
+      </c>
+      <c r="I60" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="J60" s="12">
+        <f t="shared" si="7"/>
+        <v>0.96551724137931039</v>
+      </c>
+      <c r="K60" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.96551724137931039</v>
+      </c>
+      <c r="M60" s="4">
+        <v>46237</v>
+      </c>
+      <c r="N60" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q60" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R60" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S60" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B61" s="4">
+        <v>46237</v>
+      </c>
+      <c r="C61" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F61" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G61" s="1">
+        <v>150</v>
+      </c>
+      <c r="H61" s="1">
+        <v>24</v>
+      </c>
+      <c r="I61" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.16</v>
+      </c>
+      <c r="J61" s="12">
+        <f>ABS(G$3-I61)</f>
+        <v>0.84</v>
+      </c>
+      <c r="K61" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.84</v>
+      </c>
+      <c r="M61" s="4">
+        <v>46237</v>
+      </c>
+      <c r="N61" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q61" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R61" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S61" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B62" s="4">
+        <v>46239</v>
+      </c>
+      <c r="C62" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" s="1">
+        <v>100</v>
+      </c>
+      <c r="F62" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G62" s="1">
+        <v>219</v>
+      </c>
+      <c r="H62" s="1">
+        <v>14</v>
+      </c>
+      <c r="I62" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>6.3926940639269403E-2</v>
+      </c>
+      <c r="J62" s="12">
+        <f t="shared" ref="J62:J67" si="8">ABS(G$3-I62)</f>
+        <v>0.9360730593607306</v>
+      </c>
+      <c r="K62" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.9360730593607306</v>
+      </c>
+      <c r="M62" s="4">
+        <v>46237</v>
+      </c>
+      <c r="N62" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q62" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R62" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B63" s="4">
+        <v>46239</v>
+      </c>
+      <c r="C63" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" s="1">
+        <v>150</v>
+      </c>
+      <c r="F63" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G63" s="1">
+        <v>219</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="12">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K63" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M63" s="4">
+        <v>46237</v>
+      </c>
+      <c r="N63" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P63" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q63" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R63" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S63" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B64" s="4">
+        <v>46239</v>
+      </c>
+      <c r="C64" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" s="1">
+        <v>200</v>
+      </c>
+      <c r="F64" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G64" s="1">
+        <v>216</v>
+      </c>
+      <c r="H64" s="1">
+        <v>18</v>
+      </c>
+      <c r="I64" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="J64" s="12">
+        <f t="shared" si="8"/>
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="K64" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="M64" s="4">
+        <v>46239</v>
+      </c>
+      <c r="N64" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q64" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R64" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S64" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B65" s="4">
+        <v>46239</v>
+      </c>
+      <c r="C65" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" s="1">
+        <v>300</v>
+      </c>
+      <c r="F65" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G65" s="1">
+        <v>210</v>
+      </c>
+      <c r="H65" s="1">
+        <v>8</v>
+      </c>
+      <c r="I65" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>3.8095238095238099E-2</v>
+      </c>
+      <c r="J65" s="12">
+        <f t="shared" si="8"/>
+        <v>0.96190476190476193</v>
+      </c>
+      <c r="K65" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.96190476190476193</v>
+      </c>
+      <c r="M65" s="4">
+        <v>46239</v>
+      </c>
+      <c r="N65" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q65" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R65" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S65" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B66" s="4">
+        <v>46239</v>
+      </c>
+      <c r="C66" s="12">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F66" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G66" s="1">
+        <v>187</v>
+      </c>
+      <c r="H66" s="1">
+        <v>24</v>
+      </c>
+      <c r="I66" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.12834224598930483</v>
+      </c>
+      <c r="J66" s="12">
+        <f t="shared" si="8"/>
+        <v>0.87165775401069512</v>
+      </c>
+      <c r="K66" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.87165775401069512</v>
+      </c>
+      <c r="M66" s="4">
+        <v>46239</v>
+      </c>
+      <c r="N66" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q66" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R66" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S66" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B67" s="4"/>
+      <c r="C67" s="12"/>
+      <c r="F67" s="9"/>
       <c r="I67" s="3"/>
-      <c r="J67" s="1"/>
+      <c r="J67" s="12"/>
       <c r="K67" s="5"/>
       <c r="M67" s="4"/>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B68" s="4"/>
+      <c r="G68" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="I68" s="3"/>
       <c r="J68" s="1"/>
       <c r="K68" s="5"/>
       <c r="M68" s="4"/>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B69" s="4"/>
       <c r="I69" s="3"/>
       <c r="J69" s="1"/>
       <c r="K69" s="5"/>
       <c r="M69" s="4"/>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B70" s="4"/>
       <c r="I70" s="3"/>
       <c r="J70" s="1"/>
       <c r="K70" s="5"/>
       <c r="M70" s="4"/>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B71" s="4"/>
       <c r="I71" s="3"/>
       <c r="J71" s="1"/>
       <c r="K71" s="5"/>
       <c r="M71" s="4"/>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B72" s="4"/>
       <c r="I72" s="3"/>
       <c r="J72" s="1"/>
       <c r="K72" s="5"/>
       <c r="M72" s="4"/>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B73" s="4"/>
       <c r="I73" s="3"/>
       <c r="J73" s="1"/>
       <c r="K73" s="5"/>
       <c r="M73" s="4"/>
     </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B74" s="4"/>
       <c r="I74" s="3"/>
       <c r="J74" s="1"/>
       <c r="K74" s="5"/>
       <c r="M74" s="4"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B75" s="4"/>
       <c r="I75" s="3"/>
       <c r="J75" s="1"/>
       <c r="K75" s="5"/>
       <c r="M75" s="4"/>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B76" s="4"/>
       <c r="I76" s="3"/>
       <c r="J76" s="1"/>
       <c r="K76" s="5"/>
       <c r="M76" s="4"/>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B77" s="4"/>
       <c r="I77" s="3"/>
       <c r="J77" s="1"/>
       <c r="K77" s="5"/>
       <c r="M77" s="4"/>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B78" s="4"/>
       <c r="I78" s="3"/>
       <c r="J78" s="1"/>
       <c r="K78" s="5"/>
       <c r="M78" s="4"/>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B79" s="4"/>
       <c r="I79" s="3"/>
       <c r="J79" s="1"/>
       <c r="K79" s="5"/>
       <c r="M79" s="4"/>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B80" s="4"/>
       <c r="I80" s="3"/>
       <c r="J80" s="1"/>
@@ -26849,6 +29446,8 @@
       <c r="J219" s="1"/>
       <c r="K219" s="5"/>
       <c r="M219" s="4"/>
+      <c r="U219" s="1"/>
+      <c r="V219" s="1"/>
     </row>
     <row r="220" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B220" s="4"/>
@@ -26856,6 +29455,8 @@
       <c r="J220" s="1"/>
       <c r="K220" s="5"/>
       <c r="M220" s="4"/>
+      <c r="U220" s="1"/>
+      <c r="V220" s="1"/>
     </row>
     <row r="221" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B221" s="4"/>
@@ -26863,8 +29464,6 @@
       <c r="J221" s="1"/>
       <c r="K221" s="5"/>
       <c r="M221" s="4"/>
-      <c r="U221" s="1"/>
-      <c r="V221" s="1"/>
     </row>
     <row r="222" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B222" s="4"/>
@@ -26872,8 +29471,6 @@
       <c r="J222" s="1"/>
       <c r="K222" s="5"/>
       <c r="M222" s="4"/>
-      <c r="U222" s="1"/>
-      <c r="V222" s="1"/>
     </row>
     <row r="223" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B223" s="4"/>
@@ -26971,14 +29568,14 @@
       <c r="I236" s="3"/>
       <c r="J236" s="1"/>
       <c r="K236" s="5"/>
-      <c r="M236" s="4"/>
+      <c r="M236" s="8"/>
     </row>
     <row r="237" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B237" s="4"/>
       <c r="I237" s="3"/>
       <c r="J237" s="1"/>
       <c r="K237" s="5"/>
-      <c r="M237" s="4"/>
+      <c r="M237" s="8"/>
     </row>
     <row r="238" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B238" s="4"/>
@@ -26992,14 +29589,14 @@
       <c r="I239" s="3"/>
       <c r="J239" s="1"/>
       <c r="K239" s="5"/>
-      <c r="M239" s="8"/>
+      <c r="M239" s="4"/>
     </row>
     <row r="240" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B240" s="4"/>
       <c r="I240" s="3"/>
       <c r="J240" s="1"/>
       <c r="K240" s="5"/>
-      <c r="M240" s="8"/>
+      <c r="M240" s="4"/>
     </row>
     <row r="241" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B241" s="4"/>
@@ -27278,14 +29875,12 @@
       <c r="B280" s="4"/>
       <c r="I280" s="3"/>
       <c r="J280" s="1"/>
-      <c r="K280" s="5"/>
       <c r="M280" s="4"/>
     </row>
     <row r="281" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B281" s="4"/>
       <c r="I281" s="3"/>
       <c r="J281" s="1"/>
-      <c r="K281" s="5"/>
       <c r="M281" s="4"/>
     </row>
     <row r="282" spans="2:13" x14ac:dyDescent="0.3">
@@ -27304,13 +29899,11 @@
       <c r="B284" s="4"/>
       <c r="I284" s="3"/>
       <c r="J284" s="1"/>
-      <c r="M284" s="4"/>
     </row>
     <row r="285" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B285" s="4"/>
       <c r="I285" s="3"/>
       <c r="J285" s="1"/>
-      <c r="M285" s="4"/>
     </row>
     <row r="286" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B286" s="4"/>
@@ -27393,6 +29986,9 @@
       <c r="J301" s="1"/>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>0</v>
+      </c>
       <c r="B302" s="4"/>
       <c r="I302" s="3"/>
       <c r="J302" s="1"/>
@@ -27403,9 +29999,6 @@
       <c r="J303" s="1"/>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A304" t="s">
-        <v>0</v>
-      </c>
       <c r="B304" s="4"/>
       <c r="I304" s="3"/>
       <c r="J304" s="1"/>
@@ -27596,6 +30189,9 @@
       <c r="J341" s="1"/>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>0</v>
+      </c>
       <c r="B342" s="4"/>
       <c r="I342" s="3"/>
       <c r="J342" s="1"/>
@@ -27606,9 +30202,6 @@
       <c r="J343" s="1"/>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A344" t="s">
-        <v>0</v>
-      </c>
       <c r="B344" s="4"/>
       <c r="I344" s="3"/>
       <c r="J344" s="1"/>
@@ -28022,11 +30615,17 @@
       <c r="B426" s="4"/>
       <c r="I426" s="3"/>
       <c r="J426" s="1"/>
+      <c r="M426" s="7"/>
+      <c r="N426" s="7"/>
+      <c r="O426" s="7"/>
     </row>
     <row r="427" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B427" s="4"/>
       <c r="I427" s="3"/>
       <c r="J427" s="1"/>
+      <c r="M427" s="7"/>
+      <c r="N427" s="7"/>
+      <c r="O427" s="7"/>
     </row>
     <row r="428" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B428" s="4"/>
@@ -28169,7 +30768,7 @@
       <c r="I445" s="3"/>
       <c r="J445" s="1"/>
       <c r="M445" s="7"/>
-      <c r="N445" s="7"/>
+      <c r="N445" s="8"/>
       <c r="O445" s="7"/>
     </row>
     <row r="446" spans="2:15" x14ac:dyDescent="0.3">
@@ -28185,7 +30784,7 @@
       <c r="I447" s="3"/>
       <c r="J447" s="1"/>
       <c r="M447" s="7"/>
-      <c r="N447" s="8"/>
+      <c r="N447" s="7"/>
       <c r="O447" s="7"/>
     </row>
     <row r="448" spans="2:15" x14ac:dyDescent="0.3">
@@ -28400,17 +30999,11 @@
       <c r="B474" s="4"/>
       <c r="I474" s="3"/>
       <c r="J474" s="1"/>
-      <c r="M474" s="7"/>
-      <c r="N474" s="7"/>
-      <c r="O474" s="7"/>
     </row>
     <row r="475" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B475" s="4"/>
       <c r="I475" s="3"/>
       <c r="J475" s="1"/>
-      <c r="M475" s="7"/>
-      <c r="N475" s="7"/>
-      <c r="O475" s="7"/>
     </row>
     <row r="476" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B476" s="4"/>
@@ -29438,6 +32031,9 @@
       <c r="J680" s="1"/>
     </row>
     <row r="681" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A681" t="s">
+        <v>0</v>
+      </c>
       <c r="B681" s="4"/>
       <c r="I681" s="3"/>
       <c r="J681" s="1"/>
@@ -29448,9 +32044,6 @@
       <c r="J682" s="1"/>
     </row>
     <row r="683" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A683" t="s">
-        <v>0</v>
-      </c>
       <c r="B683" s="4"/>
       <c r="I683" s="3"/>
       <c r="J683" s="1"/>
@@ -29471,6 +32064,9 @@
       <c r="J686" s="1"/>
     </row>
     <row r="687" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A687" t="s">
+        <v>0</v>
+      </c>
       <c r="B687" s="4"/>
       <c r="I687" s="3"/>
       <c r="J687" s="1"/>
@@ -29481,9 +32077,6 @@
       <c r="J688" s="1"/>
     </row>
     <row r="689" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A689" t="s">
-        <v>0</v>
-      </c>
       <c r="B689" s="4"/>
       <c r="I689" s="3"/>
       <c r="J689" s="1"/>
@@ -29504,6 +32097,9 @@
       <c r="J692" s="1"/>
     </row>
     <row r="693" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A693" t="s">
+        <v>0</v>
+      </c>
       <c r="B693" s="4"/>
       <c r="I693" s="3"/>
       <c r="J693" s="1"/>
@@ -29514,9 +32110,6 @@
       <c r="J694" s="1"/>
     </row>
     <row r="695" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A695" t="s">
-        <v>0</v>
-      </c>
       <c r="B695" s="4"/>
       <c r="I695" s="3"/>
       <c r="J695" s="1"/>
@@ -29537,6 +32130,9 @@
       <c r="J698" s="1"/>
     </row>
     <row r="699" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A699" t="s">
+        <v>0</v>
+      </c>
       <c r="B699" s="4"/>
       <c r="I699" s="3"/>
       <c r="J699" s="1"/>
@@ -29547,9 +32143,6 @@
       <c r="J700" s="1"/>
     </row>
     <row r="701" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A701" t="s">
-        <v>0</v>
-      </c>
       <c r="B701" s="4"/>
       <c r="I701" s="3"/>
       <c r="J701" s="1"/>
@@ -29570,6 +32163,9 @@
       <c r="J704" s="1"/>
     </row>
     <row r="705" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A705" t="s">
+        <v>0</v>
+      </c>
       <c r="B705" s="4"/>
       <c r="I705" s="3"/>
       <c r="J705" s="1"/>
@@ -29580,9 +32176,6 @@
       <c r="J706" s="1"/>
     </row>
     <row r="707" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A707" t="s">
-        <v>0</v>
-      </c>
       <c r="B707" s="4"/>
       <c r="I707" s="3"/>
       <c r="J707" s="1"/>
@@ -29603,6 +32196,9 @@
       <c r="J710" s="1"/>
     </row>
     <row r="711" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A711" t="s">
+        <v>0</v>
+      </c>
       <c r="B711" s="4"/>
       <c r="I711" s="3"/>
       <c r="J711" s="1"/>
@@ -29613,9 +32209,6 @@
       <c r="J712" s="1"/>
     </row>
     <row r="713" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A713" t="s">
-        <v>0</v>
-      </c>
       <c r="B713" s="4"/>
       <c r="I713" s="3"/>
       <c r="J713" s="1"/>
@@ -29655,170 +32248,173 @@
       <c r="I720" s="3"/>
       <c r="J720" s="1"/>
     </row>
-    <row r="721" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B721" s="4"/>
       <c r="I721" s="3"/>
       <c r="J721" s="1"/>
     </row>
-    <row r="722" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B722" s="4"/>
       <c r="I722" s="3"/>
       <c r="J722" s="1"/>
     </row>
-    <row r="723" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B723" s="4"/>
       <c r="I723" s="3"/>
       <c r="J723" s="1"/>
     </row>
-    <row r="724" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B724" s="4"/>
       <c r="I724" s="3"/>
       <c r="J724" s="1"/>
     </row>
-    <row r="725" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B725" s="4"/>
       <c r="I725" s="3"/>
       <c r="J725" s="1"/>
     </row>
-    <row r="726" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B726" s="4"/>
       <c r="I726" s="3"/>
       <c r="J726" s="1"/>
     </row>
-    <row r="727" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B727" s="4"/>
       <c r="I727" s="3"/>
       <c r="J727" s="1"/>
     </row>
-    <row r="728" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B728" s="4"/>
       <c r="I728" s="3"/>
       <c r="J728" s="1"/>
     </row>
-    <row r="729" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B729" s="4"/>
       <c r="I729" s="3"/>
       <c r="J729" s="1"/>
     </row>
-    <row r="730" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B730" s="4"/>
       <c r="I730" s="3"/>
       <c r="J730" s="1"/>
     </row>
-    <row r="731" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B731" s="4"/>
       <c r="I731" s="3"/>
       <c r="J731" s="1"/>
     </row>
-    <row r="732" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B732" s="4"/>
       <c r="I732" s="3"/>
       <c r="J732" s="1"/>
     </row>
-    <row r="733" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B733" s="4"/>
       <c r="I733" s="3"/>
       <c r="J733" s="1"/>
     </row>
-    <row r="734" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B734" s="4"/>
       <c r="I734" s="3"/>
       <c r="J734" s="1"/>
     </row>
-    <row r="735" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A735" t="s">
+        <v>0</v>
+      </c>
       <c r="B735" s="4"/>
       <c r="I735" s="3"/>
       <c r="J735" s="1"/>
     </row>
-    <row r="736" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B736" s="4"/>
       <c r="I736" s="3"/>
       <c r="J736" s="1"/>
     </row>
-    <row r="737" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A737" t="s">
-        <v>0</v>
-      </c>
+    <row r="737" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B737" s="4"/>
       <c r="I737" s="3"/>
       <c r="J737" s="1"/>
     </row>
-    <row r="738" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="738" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B738" s="4"/>
       <c r="I738" s="3"/>
       <c r="J738" s="1"/>
     </row>
-    <row r="739" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="739" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B739" s="4"/>
       <c r="I739" s="3"/>
       <c r="J739" s="1"/>
     </row>
-    <row r="740" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="740" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B740" s="4"/>
       <c r="I740" s="3"/>
       <c r="J740" s="1"/>
     </row>
-    <row r="741" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="741" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B741" s="4"/>
       <c r="I741" s="3"/>
       <c r="J741" s="1"/>
     </row>
-    <row r="742" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="742" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B742" s="4"/>
       <c r="I742" s="3"/>
       <c r="J742" s="1"/>
     </row>
-    <row r="743" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="743" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B743" s="4"/>
       <c r="I743" s="3"/>
       <c r="J743" s="1"/>
     </row>
-    <row r="744" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="744" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B744" s="4"/>
       <c r="I744" s="3"/>
       <c r="J744" s="1"/>
     </row>
-    <row r="745" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="745" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B745" s="4"/>
       <c r="I745" s="3"/>
       <c r="J745" s="1"/>
     </row>
-    <row r="746" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="746" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B746" s="4"/>
       <c r="I746" s="3"/>
       <c r="J746" s="1"/>
     </row>
-    <row r="747" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="747" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B747" s="4"/>
       <c r="I747" s="3"/>
       <c r="J747" s="1"/>
     </row>
-    <row r="748" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="748" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B748" s="4"/>
       <c r="I748" s="3"/>
       <c r="J748" s="1"/>
     </row>
-    <row r="749" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="749" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B749" s="4"/>
       <c r="I749" s="3"/>
       <c r="J749" s="1"/>
     </row>
-    <row r="750" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="750" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B750" s="4"/>
       <c r="I750" s="3"/>
       <c r="J750" s="1"/>
     </row>
-    <row r="751" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="751" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B751" s="4"/>
       <c r="I751" s="3"/>
       <c r="J751" s="1"/>
     </row>
-    <row r="752" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="752" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B752" s="4"/>
       <c r="I752" s="3"/>
       <c r="J752" s="1"/>
     </row>
     <row r="753" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A753" t="s">
+        <v>0</v>
+      </c>
       <c r="B753" s="4"/>
       <c r="I753" s="3"/>
       <c r="J753" s="1"/>
@@ -29829,9 +32425,6 @@
       <c r="J754" s="1"/>
     </row>
     <row r="755" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A755" t="s">
-        <v>0</v>
-      </c>
       <c r="B755" s="4"/>
       <c r="I755" s="3"/>
       <c r="J755" s="1"/>
@@ -30002,7 +32595,6 @@
       <c r="J788" s="1"/>
     </row>
     <row r="789" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B789" s="4"/>
       <c r="I789" s="3"/>
       <c r="J789" s="1"/>
     </row>
@@ -30012,6 +32604,7 @@
       <c r="J790" s="1"/>
     </row>
     <row r="791" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B791" s="4"/>
       <c r="I791" s="3"/>
       <c r="J791" s="1"/>
     </row>
@@ -30062,6 +32655,7 @@
     </row>
     <row r="801" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B801" s="4"/>
+      <c r="G801" s="4"/>
       <c r="I801" s="3"/>
       <c r="J801" s="1"/>
     </row>
@@ -30072,7 +32666,6 @@
     </row>
     <row r="803" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B803" s="4"/>
-      <c r="G803" s="4"/>
       <c r="I803" s="3"/>
       <c r="J803" s="1"/>
     </row>
@@ -30200,16 +32793,6 @@
       <c r="B828" s="4"/>
       <c r="I828" s="3"/>
       <c r="J828" s="1"/>
-    </row>
-    <row r="829" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B829" s="4"/>
-      <c r="I829" s="3"/>
-      <c r="J829" s="1"/>
-    </row>
-    <row r="830" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B830" s="4"/>
-      <c r="I830" s="3"/>
-      <c r="J830" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\5_MB MMA\09_Information\10_FTQ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\4_NX5a\09_Information\10_FTQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56EEF4C1-FB27-406C-9DD0-4949BCBF9368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81C1498-AB3E-42BA-9099-F89FB4C26158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
   </bookViews>
   <sheets>
-    <sheet name="BASE DE DATOS" sheetId="1" r:id="rId1"/>
+    <sheet name="BASE DE DATOS RIVIAN" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS RIVIAN'!$B$4:$J$62</definedName>
     <definedName name="DATA_01">[1]Data_Lineal!$H$4:$Y$30</definedName>
     <definedName name="DB_01">#REF!</definedName>
     <definedName name="DB_CAP01">'[2]CAPACIDAD (1)'!$X$9:$AM$29</definedName>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="51">
   <si>
     <t>*</t>
   </si>
@@ -111,136 +111,112 @@
     <t>PRODUCCIÓN</t>
   </si>
   <si>
-    <t>SCR MMA</t>
+    <t>1100A</t>
   </si>
   <si>
-    <t>EOL</t>
+    <t>Falso rechazo Op.1100A</t>
   </si>
   <si>
-    <t>Mal enrollado de cables Op.200</t>
+    <t>1100B</t>
   </si>
   <si>
-    <t>Mal ensamble con cable AB dañado Op.150</t>
+    <t>Hyundai/KIA</t>
   </si>
   <si>
-    <t>Mala colocación de cable AB en doblez Op.150</t>
+    <t>Falta de puntos de grasa Op.100</t>
   </si>
   <si>
-    <t>Cables dañados por doblez Op.150</t>
+    <t>Corredera mal posicionada Op.400</t>
   </si>
   <si>
-    <t>Falla en inspección visual no detecta piezas NOK Op.200</t>
+    <t>Corto de soldadura Op.800</t>
   </si>
   <si>
-    <t>Latch y Resorte no llegan a posición correcta Op.300</t>
+    <t>Falta de soldadura Op.800</t>
   </si>
   <si>
-    <t>Falla 3320.041 Op.EOL</t>
+    <t>Falta de soldadura Op.1100A</t>
   </si>
   <si>
-    <t>Falla 3310.011 Op.EOL</t>
+    <t>Lever Barcode Scan Facture Op.300</t>
   </si>
   <si>
-    <t>Falsos rechazos Op.EOL</t>
+    <t>Falla en lectura de Scanner Op.300</t>
   </si>
   <si>
-    <t>Falla 3550.002 Op.EOL</t>
+    <t>Falla de inspección visual Op.200</t>
   </si>
   <si>
-    <t>Falla 6000.001 Op.EOL</t>
+    <t>Falla de inspección visual Op.300</t>
   </si>
   <si>
-    <t>Falla 2110.020 Op.EOL</t>
+    <t>Falla de inspección visual Op.600</t>
   </si>
   <si>
-    <t>Cable and Mark NG (Ventanita) Op.EOL</t>
+    <t>Falla de inspección visual Op.400</t>
   </si>
   <si>
-    <t>SCCM MMA</t>
+    <t>Falla en lectura de Scanner Op.400</t>
   </si>
   <si>
-    <t>Falla de inspección visual en curvas sin NG Op.100</t>
+    <t>Falla en atornillado Op.700</t>
   </si>
   <si>
-    <t>Falla por falta de caída de SAS por gravedad sin NG Op.200</t>
+    <t>Falla sin especificación Op.900</t>
   </si>
   <si>
-    <t>Dispensado de Grasa No Uniforme en Engrane sin NG Op.200</t>
+    <t>Mal embobinado en spiral Op.1100A</t>
   </si>
   <si>
-    <t>Sensor no detecta mesa giratoria Op.400</t>
+    <t>Falla de sensor de slai Op.400</t>
   </si>
   <si>
-    <t>Falla en inspección visual de Ruteo de Arnes Op.700</t>
+    <t>Falla de sensor S$9 Op.400</t>
   </si>
   <si>
-    <t>Falla en alimentador de Tornillos Op.800</t>
+    <t>Material Towerdid Op.400</t>
   </si>
   <si>
-    <t>Falla de inspección visual en Mordaza Métalica sin NG Op.100</t>
+    <t xml:space="preserve">SFC 965827AGG00003 is not in queue at operation Op.400 </t>
   </si>
   <si>
-    <t>Falla de Etiqueta por Guarda sin NG Op.300</t>
+    <t>Sin especificar Op. 600</t>
   </si>
   <si>
-    <t>Falla de inspección visual  Op.600</t>
+    <t>Sin especificar ok Op. 600</t>
   </si>
   <si>
-    <t>Inspección visual  no detecta PCB sin conector Op.600</t>
+    <t>Falso Rechazo (version de SCR) Op.700</t>
   </si>
   <si>
-    <t>Falla de inspección visual  Op.700</t>
+    <t>Falta de grasa en PCB Op.400</t>
   </si>
   <si>
-    <t>No pide Inspección visual  del SCAS Op.700</t>
+    <t>Detecta piezas de sobre-producción Op.400</t>
   </si>
   <si>
-    <t>Mal enclipsado de Engrane en Housing (SAS) Op.200</t>
+    <t>Mezcla de material con index incorrecto Op.700</t>
   </si>
   <si>
-    <t>Falla de Robot de enclipsado de Engrane en Housing (SAS) Op.200</t>
+    <t>Falla 0090.040 Op.1100A</t>
   </si>
   <si>
-    <t>Falla Mécanica en nido giratorio Op.500</t>
+    <t>Falla  0040.074 Op.1100A</t>
   </si>
   <si>
-    <t>Falla de inspección visual en Stator Housing Op.100</t>
+    <t>Falla 0400.020 Op.1100A</t>
   </si>
   <si>
-    <t>Falla de inspección visual en Rotor Housing Op.100</t>
+    <t>Falla 0400.030 Op.1100A</t>
   </si>
   <si>
-    <t>Falla de altura de cable AB Op.200</t>
+    <t>Falla 0060.005 Op.1100A</t>
   </si>
   <si>
-    <t>Cable Dummy dañado Op.200</t>
+    <t>Falla 0090.004 Op.1100B</t>
   </si>
   <si>
-    <t>Falla "Codigo de barra no corresponde a la versión"  sin NOK Op.300</t>
-  </si>
-  <si>
-    <t>Falla 3110.004 Op.EOL</t>
-  </si>
-  <si>
-    <t>Falla 2270.004 Op.EOL</t>
-  </si>
-  <si>
-    <t>Falla de inspección visual no permite colocar Bearing Ring Op.100</t>
-  </si>
-  <si>
-    <t>Falla 2110.010 Op.EOL</t>
-  </si>
-  <si>
-    <t>Falla 2230.011 Op.EOL</t>
-  </si>
-  <si>
-    <t>Falla 3310.251 Op.EOL</t>
-  </si>
-  <si>
-    <t>Falla 3121.022 Op.EOL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <t>Detecta pieza sin pasar en operación anterior Op.700</t>
   </si>
 </sst>
 </file>
@@ -24345,7 +24321,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K66" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K62" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CDAA4D20-2955-41E2-BD7E-9330E166FFF4}" name="Fecha" dataDxfId="18"/>
     <tableColumn id="9" xr3:uid="{F70BB124-92DE-4024-874C-EE3BA966CDE6}" name="Semana" dataDxfId="17">
@@ -24371,7 +24347,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S66" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S61" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D688BA2E-A64E-4433-85E0-7EDBF854AF60}" name="Fecha" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{D3EA5E8D-DD68-48AC-8DAC-4A4077839479}" name="Semana" dataDxfId="5">
@@ -24650,7 +24626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A1B645-8848-474A-88BA-FA9209B01B4F}">
-  <dimension ref="A1:V828"/>
+  <dimension ref="A1:V830"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
@@ -24660,7 +24636,7 @@
     <col min="6" max="7" width="11.5546875" style="1"/>
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="0" style="2" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="11.5546875" style="2"/>
     <col min="12" max="12" width="2.44140625" customWidth="1"/>
     <col min="13" max="13" width="13.88671875" style="1" customWidth="1"/>
@@ -24668,7 +24644,7 @@
     <col min="15" max="15" width="12.44140625" style="1" customWidth="1"/>
     <col min="16" max="16" width="13.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="50.44140625" style="1" customWidth="1"/>
     <col min="19" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -24777,115 +24753,115 @@
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B5" s="4">
-        <v>46224</v>
+        <v>46217</v>
       </c>
       <c r="C5" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1">
         <v>100</v>
       </c>
       <c r="F5" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="G5" s="1">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>9.6153846153846159E-3</v>
       </c>
       <c r="J5" s="1">
-        <f t="shared" ref="J5:J9" si="0">ABS(G$3-I5)</f>
-        <v>1</v>
+        <f t="shared" ref="J5:J13" si="0">ABS(G$3-I5)</f>
+        <v>0.99038461538461542</v>
       </c>
       <c r="K5" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.99038461538461542</v>
       </c>
       <c r="M5" s="4">
-        <v>46224</v>
+        <v>46217</v>
       </c>
       <c r="N5" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P5" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q5" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B6" s="4">
-        <v>46224</v>
+        <v>46217</v>
       </c>
       <c r="C6" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E6" s="1">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F6" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="G6" s="1">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>9.433962264150943E-3</v>
       </c>
       <c r="J6" s="1">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.99056603773584906</v>
       </c>
       <c r="K6" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.99056603773584906</v>
       </c>
       <c r="M6" s="4">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="N6" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P6" s="1">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="Q6" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="S6" s="1">
         <v>1</v>
@@ -24893,344 +24869,344 @@
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
-        <v>46224</v>
+        <v>46217</v>
       </c>
       <c r="C7" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F7" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="G7" s="1">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="H7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.11764705882352941</v>
+        <v>2.6785714285714284E-2</v>
       </c>
       <c r="J7" s="1">
         <f t="shared" si="0"/>
-        <v>0.88235294117647056</v>
+        <v>0.9732142857142857</v>
       </c>
       <c r="K7" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.88235294117647056</v>
+        <v>0.9732142857142857</v>
       </c>
       <c r="M7" s="4">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="N7" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P7" s="1">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="Q7" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="S7" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
-        <v>46224</v>
+        <v>46217</v>
       </c>
       <c r="C8" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F8" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="G8" s="1">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="I8" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.84042553191489366</v>
       </c>
       <c r="J8" s="1">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.15957446808510634</v>
       </c>
       <c r="K8" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.15957446808510634</v>
       </c>
       <c r="M8" s="4">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="N8" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P8" s="1">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="Q8" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="R8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="S8" s="1">
-        <v>7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="C9" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F9" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="G9" s="1">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>1.0309278350515464E-2</v>
       </c>
       <c r="J9" s="1">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.98969072164948457</v>
       </c>
       <c r="K9" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.98969072164948457</v>
       </c>
       <c r="M9" s="4">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="N9" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P9" s="1">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="Q9" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="S9" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="C10" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="F10" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="G10" s="1">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="H10" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.12676056338028169</v>
+        <v>0</v>
       </c>
       <c r="J10" s="1">
-        <f t="shared" ref="J10:J12" si="1">ABS(G$3-I10)</f>
-        <v>0.87323943661971826</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="K10" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.87323943661971826</v>
+        <v>1</v>
       </c>
       <c r="M10" s="4">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="N10" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P10" s="1">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="Q10" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="S10" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="C11" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E11" s="1">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="F11" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="G11" s="1">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="H11" s="1">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I11" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>5.9701492537313432E-2</v>
+        <v>0.12244897959183673</v>
       </c>
       <c r="J11" s="1">
-        <f t="shared" si="1"/>
-        <v>0.94029850746268662</v>
+        <f t="shared" si="0"/>
+        <v>0.87755102040816324</v>
       </c>
       <c r="K11" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.94029850746268662</v>
+        <v>0.87755102040816324</v>
       </c>
       <c r="M11" s="4">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="N11" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P11" s="1">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="Q11" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>22</v>
       </c>
       <c r="S11" s="1">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="C12" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E12" s="1">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="F12" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="G12" s="1">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="H12" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I12" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.78260869565217395</v>
+        <v>0</v>
       </c>
       <c r="J12" s="1">
-        <f t="shared" si="1"/>
-        <v>0.21739130434782605</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="K12" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.21739130434782605</v>
+        <v>1</v>
       </c>
       <c r="M12" s="4">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="N12" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P12" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="Q12" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>23</v>
@@ -25241,57 +25217,57 @@
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="C13" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F13" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="G13" s="1">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="H13" s="1">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I13" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.2391304347826087</v>
+        <v>3.896103896103896E-2</v>
       </c>
       <c r="J13" s="1">
-        <f>ABS(G$3-I13)</f>
-        <v>0.76086956521739135</v>
+        <f t="shared" si="0"/>
+        <v>0.96103896103896103</v>
       </c>
       <c r="K13" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.76086956521739135</v>
+        <v>0.96103896103896103</v>
       </c>
       <c r="M13" s="4">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="N13" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P13" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="Q13" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S13" s="1">
         <v>1</v>
@@ -25299,23 +25275,23 @@
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B14" s="4">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="C14" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E14" s="1">
         <v>100</v>
       </c>
       <c r="F14" s="9">
-        <v>12289497</v>
+        <v>12264732</v>
       </c>
       <c r="G14" s="1">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="H14" s="1">
         <v>0</v>
@@ -25325,7 +25301,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <f t="shared" ref="J14:J24" si="2">ABS(G$3-I14)</f>
+        <f t="shared" ref="J14:J22" si="1">ABS(G$3-I14)</f>
         <v>1</v>
       </c>
       <c r="K14" s="5">
@@ -25333,511 +25309,511 @@
         <v>1</v>
       </c>
       <c r="M14" s="4">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="N14" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P14" s="1" t="s">
+      <c r="Q14" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Q14" s="9">
-        <v>10532587</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="S14" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="C15" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E15" s="1">
         <v>200</v>
       </c>
       <c r="F15" s="9">
-        <v>12289497</v>
+        <v>12264732</v>
       </c>
       <c r="G15" s="1">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="H15" s="1">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I15" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.4</v>
+        <v>4.9180327868852458E-2</v>
       </c>
       <c r="J15" s="1">
-        <f t="shared" si="2"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.95081967213114749</v>
       </c>
       <c r="K15" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.6</v>
+        <v>0.95081967213114749</v>
       </c>
       <c r="M15" s="4">
-        <v>46226</v>
+        <v>46220</v>
       </c>
       <c r="N15" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="P15" s="1">
+        <v>200</v>
       </c>
       <c r="Q15" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="S15" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B16" s="4">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="C16" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E16" s="1">
         <v>300</v>
       </c>
       <c r="F16" s="9">
-        <v>12289497</v>
+        <v>12264732</v>
       </c>
       <c r="G16" s="1">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I16" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J16" s="1">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.7142857142857143</v>
       </c>
       <c r="K16" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="M16" s="4">
-        <v>46226</v>
+        <v>46220</v>
       </c>
       <c r="N16" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="P16" s="1">
+        <v>300</v>
       </c>
       <c r="Q16" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="S16" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B17" s="4">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="C17" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E17" s="1">
         <v>400</v>
       </c>
       <c r="F17" s="9">
-        <v>12289497</v>
+        <v>12264732</v>
       </c>
       <c r="G17" s="1">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I17" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.45454545454545453</v>
       </c>
       <c r="J17" s="1">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.54545454545454541</v>
       </c>
       <c r="K17" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="M17" s="4">
-        <v>46226</v>
+        <v>46220</v>
       </c>
       <c r="N17" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="P17" s="1">
+        <v>300</v>
       </c>
       <c r="Q17" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S17" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B18" s="4">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="C18" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E18" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F18" s="9">
-        <v>12289497</v>
+        <v>12264732</v>
       </c>
       <c r="G18" s="1">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I18" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.1038961038961039</v>
       </c>
       <c r="J18" s="1">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.89610389610389607</v>
       </c>
       <c r="K18" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.89610389610389607</v>
       </c>
       <c r="M18" s="4">
-        <v>46226</v>
+        <v>46220</v>
       </c>
       <c r="N18" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="P18" s="1">
+        <v>300</v>
       </c>
       <c r="Q18" s="9">
-        <v>10532587</v>
+        <v>12264732</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="S18" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="C19" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E19" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F19" s="9">
-        <v>12289497</v>
+        <v>12264732</v>
       </c>
       <c r="G19" s="1">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I19" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>8.1967213114754092E-2</v>
       </c>
       <c r="J19" s="1">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.91803278688524592</v>
       </c>
       <c r="K19" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.91803278688524592</v>
       </c>
       <c r="M19" s="4">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="N19" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P19" s="1">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="Q19" s="9">
-        <v>12289497</v>
+        <v>12264732</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="S19" s="1">
-        <v>230</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
-        <v>46231</v>
+        <v>46220</v>
       </c>
       <c r="C20" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E20" s="1">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="F20" s="9">
-        <v>12289497</v>
+        <v>12264732</v>
       </c>
       <c r="G20" s="1">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="H20" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.22222222222222221</v>
+        <v>5.4545454545454543E-2</v>
       </c>
       <c r="J20" s="1">
-        <f t="shared" si="2"/>
-        <v>0.77777777777777779</v>
+        <f t="shared" si="1"/>
+        <v>0.94545454545454544</v>
       </c>
       <c r="K20" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.77777777777777779</v>
+        <v>0.94545454545454544</v>
       </c>
       <c r="M20" s="4">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="N20" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P20" s="1">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Q20" s="9">
-        <v>12289497</v>
+        <v>12264732</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="S20" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B21" s="4">
-        <v>46231</v>
+        <v>46220</v>
       </c>
       <c r="C21" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E21" s="1">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="F21" s="9">
-        <v>12289497</v>
+        <v>12264732</v>
       </c>
       <c r="G21" s="1">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I21" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>7.2727272727272724E-2</v>
       </c>
       <c r="J21" s="1">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.92727272727272725</v>
       </c>
       <c r="K21" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.92727272727272725</v>
       </c>
       <c r="M21" s="4">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="N21" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P21" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q21" s="9">
+        <v>12264732</v>
+      </c>
+      <c r="R21" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="P21" s="1">
-        <v>200</v>
-      </c>
-      <c r="Q21" s="9">
-        <v>12289497</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="S21" s="1">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B22" s="4">
-        <v>46231</v>
+        <v>46220</v>
       </c>
       <c r="C22" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="1">
-        <v>300</v>
+        <v>18</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="F22" s="9">
-        <v>12289497</v>
+        <v>12264732</v>
       </c>
       <c r="G22" s="1">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H22" s="1">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I22" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.28260869565217389</v>
+        <v>2.7777777777777776E-2</v>
       </c>
       <c r="J22" s="1">
-        <f t="shared" si="2"/>
-        <v>0.71739130434782616</v>
+        <f t="shared" si="1"/>
+        <v>0.97222222222222221</v>
       </c>
       <c r="K22" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.71739130434782616</v>
+        <v>0.97222222222222221</v>
       </c>
       <c r="M22" s="4">
-        <v>46231</v>
+        <v>46220</v>
       </c>
       <c r="N22" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P22" s="1">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="Q22" s="9">
-        <v>12289497</v>
+        <v>12264732</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="S22" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B23" s="4">
-        <v>46231</v>
+        <v>46220</v>
       </c>
       <c r="C23" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="1">
-        <v>400</v>
+        <v>18</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F23" s="9">
-        <v>12289497</v>
+        <v>12264732</v>
       </c>
       <c r="G23" s="1">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
@@ -25847,7 +25823,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <f t="shared" si="2"/>
+        <f>ABS(G$3-I23)</f>
         <v>1</v>
       </c>
       <c r="K23" s="5">
@@ -25855,47 +25831,47 @@
         <v>1</v>
       </c>
       <c r="M23" s="4">
-        <v>46231</v>
+        <v>46220</v>
       </c>
       <c r="N23" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P23" s="1">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Q23" s="9">
-        <v>12289497</v>
+        <v>12264732</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S23" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B24" s="4">
-        <v>46231</v>
+        <v>46220</v>
       </c>
       <c r="C24" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E24" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F24" s="9">
-        <v>12289497</v>
+        <v>12264714</v>
       </c>
       <c r="G24" s="1">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
@@ -25905,7 +25881,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="J24:J32" si="2">ABS(G$3-I24)</f>
         <v>1</v>
       </c>
       <c r="K24" s="5">
@@ -25913,47 +25889,47 @@
         <v>1</v>
       </c>
       <c r="M24" s="4">
-        <v>46231</v>
+        <v>46220</v>
       </c>
       <c r="N24" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P24" s="1">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="Q24" s="9">
-        <v>12289497</v>
+        <v>12264732</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S24" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B25" s="4">
-        <v>46231</v>
+        <v>46220</v>
       </c>
       <c r="C25" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E25" s="1">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="F25" s="9">
-        <v>12289497</v>
+        <v>12264714</v>
       </c>
       <c r="G25" s="1">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -25963,7 +25939,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <f t="shared" ref="J25:J32" si="3">ABS(G$3-I25)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K25" s="5">
@@ -25971,221 +25947,221 @@
         <v>1</v>
       </c>
       <c r="M25" s="4">
-        <v>46231</v>
+        <v>46220</v>
       </c>
       <c r="N25" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P25" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="Q25" s="9">
-        <v>12289497</v>
+        <v>12264714</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="S25" s="1">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
-        <v>46231</v>
+        <v>46220</v>
       </c>
       <c r="C26" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E26" s="1">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="F26" s="9">
-        <v>12289497</v>
+        <v>12264714</v>
       </c>
       <c r="G26" s="1">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="H26" s="1">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.77777777777777779</v>
+        <v>0</v>
       </c>
       <c r="J26" s="1">
-        <f t="shared" si="3"/>
-        <v>0.22222222222222221</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="K26" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.22222222222222221</v>
+        <v>1</v>
       </c>
       <c r="M26" s="4">
-        <v>46231</v>
+        <v>46220</v>
       </c>
       <c r="N26" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P26" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="Q26" s="9">
-        <v>12289497</v>
+        <v>12264732</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="S26" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B27" s="4">
-        <v>46231</v>
+        <v>46220</v>
       </c>
       <c r="C27" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E27" s="1">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="F27" s="9">
-        <v>12289497</v>
+        <v>12264714</v>
       </c>
       <c r="G27" s="1">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="H27" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>6.6666666666666666E-2</v>
+        <v>0</v>
       </c>
       <c r="J27" s="1">
-        <f t="shared" si="3"/>
-        <v>0.93333333333333335</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="K27" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.93333333333333335</v>
+        <v>1</v>
       </c>
       <c r="M27" s="4">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="N27" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P27" s="1">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="Q27" s="9">
-        <v>12289475</v>
+        <v>12264732</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>31</v>
       </c>
       <c r="S27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B28" s="4">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="C28" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E28" s="1">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F28" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="G28" s="1">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="H28" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I28" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>7.9207920792079209E-2</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="J28" s="1">
-        <f t="shared" si="3"/>
-        <v>0.92079207920792083</v>
+        <f t="shared" si="2"/>
+        <v>0.93333333333333335</v>
       </c>
       <c r="K28" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.92079207920792083</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="M28" s="4">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="N28" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P28" s="1">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="Q28" s="9">
-        <v>12289475</v>
+        <v>12264732</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="S28" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B29" s="4">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="C29" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E29" s="1">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="F29" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="G29" s="1">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -26195,7 +26171,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K29" s="5">
@@ -26203,163 +26179,163 @@
         <v>1</v>
       </c>
       <c r="M29" s="4">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="N29" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P29" s="1">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="Q29" s="9">
-        <v>12289475</v>
+        <v>12264732</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="S29" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B30" s="4">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="C30" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E30" s="1">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="F30" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="G30" s="1">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="H30" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I30" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="J30" s="1">
-        <f t="shared" si="3"/>
-        <v>0.97</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="K30" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="M30" s="4">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="N30" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P30" s="1">
-        <v>400</v>
+        <v>18</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="Q30" s="9">
-        <v>12289475</v>
+        <v>12264732</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="S30" s="1">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="C31" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E31" s="1">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="F31" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="G31" s="1">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="H31" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I31" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.18965517241379309</v>
+        <v>0</v>
       </c>
       <c r="J31" s="1">
-        <f t="shared" si="3"/>
-        <v>0.81034482758620685</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="K31" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.81034482758620685</v>
+        <v>1</v>
       </c>
       <c r="M31" s="4">
-        <v>46234</v>
-      </c>
-      <c r="N31" s="1">
+        <v>46223</v>
+      </c>
+      <c r="N31" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P31" s="1">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="Q31" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="S31" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="C32" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="1">
-        <v>500</v>
+        <v>18</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="F32" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="G32" s="1">
-        <v>94</v>
+        <v>3</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -26369,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K32" s="5">
@@ -26377,511 +26353,511 @@
         <v>1</v>
       </c>
       <c r="M32" s="4">
-        <v>46234</v>
-      </c>
-      <c r="N32" s="1">
+        <v>46223</v>
+      </c>
+      <c r="N32" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P32" s="1">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="Q32" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="S32" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B33" s="4">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="C33" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E33" s="1">
-        <v>600</v>
+        <v>18</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F33" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="G33" s="1">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="H33" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I33" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>5.3191489361702128E-2</v>
+        <v>0</v>
       </c>
       <c r="J33" s="1">
-        <f t="shared" ref="J33:J37" si="4">ABS(G$3-I33)</f>
-        <v>0.94680851063829785</v>
+        <f>ABS(G$3-I33)</f>
+        <v>1</v>
       </c>
       <c r="K33" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.94680851063829785</v>
+        <v>1</v>
       </c>
       <c r="M33" s="4">
-        <v>46234</v>
-      </c>
-      <c r="N33" s="1">
+        <v>46223</v>
+      </c>
+      <c r="N33" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P33" s="1">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="Q33" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="S33" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
-        <v>46234</v>
+        <v>46223</v>
       </c>
       <c r="C34" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E34" s="1">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="F34" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="G34" s="1">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="H34" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I34" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>4.2553191489361701E-2</v>
+        <v>0</v>
       </c>
       <c r="J34" s="1">
-        <f t="shared" si="4"/>
-        <v>0.95744680851063835</v>
+        <f t="shared" ref="J34:J44" si="3">ABS(G$3-I34)</f>
+        <v>1</v>
       </c>
       <c r="K34" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.95744680851063835</v>
+        <v>1</v>
       </c>
       <c r="M34" s="4">
-        <v>46234</v>
-      </c>
-      <c r="N34" s="1">
+        <v>46223</v>
+      </c>
+      <c r="N34" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P34" s="1">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="Q34" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="S34" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B35" s="4">
-        <v>46234</v>
+        <v>46223</v>
       </c>
       <c r="C35" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E35" s="1">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="F35" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="G35" s="1">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="H35" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>1.4492753623188406E-2</v>
       </c>
       <c r="J35" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0.98550724637681164</v>
       </c>
       <c r="K35" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.98550724637681164</v>
+      </c>
+      <c r="M35" s="4">
+        <v>46223</v>
+      </c>
+      <c r="N35" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P35" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q35" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S35" s="1">
         <v>1</v>
-      </c>
-      <c r="M35" s="4">
-        <v>46238</v>
-      </c>
-      <c r="N35" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P35" s="1">
-        <v>200</v>
-      </c>
-      <c r="Q35" s="9">
-        <v>12289497</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="S35" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="36" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B36" s="4">
-        <v>46238</v>
+        <v>46223</v>
       </c>
       <c r="C36" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E36" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F36" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="G36" s="1">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="H36" s="1">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I36" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.84615384615384615</v>
+        <v>6.0606060606060608E-2</v>
       </c>
       <c r="J36" s="1">
-        <f t="shared" si="4"/>
-        <v>0.15384615384615385</v>
+        <f t="shared" si="3"/>
+        <v>0.93939393939393945</v>
       </c>
       <c r="K36" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.15384615384615385</v>
+        <v>0.93939393939393945</v>
       </c>
       <c r="M36" s="4">
-        <v>46238</v>
-      </c>
-      <c r="N36" s="1">
+        <v>46223</v>
+      </c>
+      <c r="N36" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P36" s="1">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Q36" s="9">
-        <v>12289497</v>
+        <v>12264714</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S36" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B37" s="4">
-        <v>46238</v>
+        <v>46223</v>
       </c>
       <c r="C37" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E37" s="1">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F37" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="G37" s="1">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I37" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="J37" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0.52</v>
       </c>
       <c r="K37" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.52</v>
       </c>
       <c r="M37" s="4">
-        <v>46238</v>
-      </c>
-      <c r="N37" s="1">
+        <v>46223</v>
+      </c>
+      <c r="N37" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P37" s="1">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="Q37" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="S37" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B38" s="4">
-        <v>46238</v>
+        <v>46223</v>
       </c>
       <c r="C38" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E38" s="1">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F38" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="G38" s="1">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H38" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I38" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.11428571428571428</v>
       </c>
       <c r="J38" s="1">
-        <f t="shared" ref="J38:J45" si="5">ABS(G$3-I38)</f>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0.88571428571428568</v>
       </c>
       <c r="K38" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.88571428571428568</v>
       </c>
       <c r="M38" s="4">
-        <v>46238</v>
-      </c>
-      <c r="N38" s="1">
+        <v>46223</v>
+      </c>
+      <c r="N38" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P38" s="1">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="Q38" s="9">
-        <v>12289497</v>
+        <v>12264714</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="S38" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B39" s="4">
-        <v>46238</v>
+        <v>46223</v>
       </c>
       <c r="C39" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E39" s="1">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="F39" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="G39" s="1">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H39" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I39" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.25714285714285712</v>
       </c>
       <c r="J39" s="1">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0.74285714285714288</v>
       </c>
       <c r="K39" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.74285714285714288</v>
+      </c>
+      <c r="M39" s="4">
+        <v>46223</v>
+      </c>
+      <c r="N39" s="12">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P39" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q39" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S39" s="1">
         <v>1</v>
-      </c>
-      <c r="M39" s="4">
-        <v>46238</v>
-      </c>
-      <c r="N39" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
-      </c>
-      <c r="O39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P39" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q39" s="9">
-        <v>12289475</v>
-      </c>
-      <c r="R39" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="S39" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B40" s="4">
-        <v>46238</v>
+        <v>46223</v>
       </c>
       <c r="C40" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E40" s="1">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="F40" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="G40" s="1">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H40" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I40" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J40" s="1">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0.6</v>
       </c>
       <c r="K40" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M40" s="4">
-        <v>46238</v>
-      </c>
-      <c r="N40" s="1">
+        <v>46223</v>
+      </c>
+      <c r="N40" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P40" s="1">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="Q40" s="9">
-        <v>12289497</v>
+        <v>12264714</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S40" s="1">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
-        <v>46238</v>
+        <v>46223</v>
       </c>
       <c r="C41" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E41" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="F41" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="G41" s="1">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
@@ -26891,7 +26867,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K41" s="5">
@@ -26899,47 +26875,47 @@
         <v>1</v>
       </c>
       <c r="M41" s="4">
-        <v>46238</v>
-      </c>
-      <c r="N41" s="1">
+        <v>46223</v>
+      </c>
+      <c r="N41" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P41" s="1">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="Q41" s="9">
-        <v>12289497</v>
+        <v>12264714</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="S41" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B42" s="4">
-        <v>46238</v>
+        <v>46223</v>
       </c>
       <c r="C42" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E42" s="1">
-        <v>700</v>
+        <v>18</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="F42" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="G42" s="1">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -26949,7 +26925,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K42" s="5">
@@ -26957,47 +26933,47 @@
         <v>1</v>
       </c>
       <c r="M42" s="4">
-        <v>46232</v>
+        <v>46223</v>
       </c>
       <c r="N42" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P42" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q42" s="9">
+        <v>12264714</v>
+      </c>
+      <c r="R42" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O42" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P42" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q42" s="9">
-        <v>10532587</v>
-      </c>
-      <c r="R42" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="S42" s="1">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B43" s="4">
-        <v>46238</v>
+        <v>46223</v>
       </c>
       <c r="C43" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E43" s="1">
-        <v>800</v>
+        <v>18</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F43" s="9">
-        <v>12289475</v>
+        <v>12264714</v>
       </c>
       <c r="G43" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -27007,7 +26983,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K43" s="5">
@@ -27015,255 +26991,255 @@
         <v>1</v>
       </c>
       <c r="M43" s="4">
-        <v>46232</v>
-      </c>
-      <c r="N43" s="12">
+        <v>46223</v>
+      </c>
+      <c r="N43" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P43" s="1">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="Q43" s="9">
-        <v>10532587</v>
+        <v>12264714</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="S43" s="1">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
-        <v>46238</v>
+        <v>46227</v>
       </c>
       <c r="C44" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E44" s="1">
         <v>100</v>
       </c>
       <c r="F44" s="9">
-        <v>12289497</v>
+        <v>12260416</v>
       </c>
       <c r="G44" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H44" s="1">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I44" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J44" s="1">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="K44" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M44" s="4">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="N44" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P44" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q44" s="9">
-        <v>10532587</v>
+        <v>12260416</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="S44" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B45" s="4">
-        <v>46238</v>
-      </c>
-      <c r="C45" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C45" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E45" s="1">
         <v>200</v>
       </c>
       <c r="F45" s="9">
-        <v>12289497</v>
+        <v>12260416</v>
       </c>
       <c r="G45" s="1">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="H45" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I45" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.21428571428571427</v>
-      </c>
-      <c r="J45" s="1">
-        <f t="shared" si="5"/>
-        <v>0.7857142857142857</v>
+        <v>0.04</v>
+      </c>
+      <c r="J45" s="12">
+        <f t="shared" ref="J45:J52" si="4">ABS(G$3-I45)</f>
+        <v>0.96</v>
       </c>
       <c r="K45" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.7857142857142857</v>
+        <v>0.96</v>
       </c>
       <c r="M45" s="4">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="N45" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P45" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q45" s="9">
-        <v>10532587</v>
+        <v>12260416</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="S45" s="1">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B46" s="4">
-        <v>46238</v>
-      </c>
-      <c r="C46" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C46" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E46" s="1">
         <v>300</v>
       </c>
       <c r="F46" s="9">
-        <v>12289497</v>
+        <v>12260416</v>
       </c>
       <c r="G46" s="1">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="H46" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I46" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
-      </c>
-      <c r="J46" s="1">
-        <f t="shared" ref="J46:J51" si="6">ABS(G$3-I46)</f>
-        <v>1</v>
+        <v>0.25</v>
+      </c>
+      <c r="J46" s="12">
+        <f t="shared" si="4"/>
+        <v>0.75</v>
       </c>
       <c r="K46" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M46" s="4">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="N46" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P46" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q46" s="9">
-        <v>10532587</v>
+        <v>12260416</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="S46" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
-        <v>46238</v>
-      </c>
-      <c r="C47" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C47" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E47" s="1">
         <v>400</v>
       </c>
       <c r="F47" s="9">
-        <v>12289497</v>
+        <v>12260416</v>
       </c>
       <c r="G47" s="1">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H47" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I47" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
-      </c>
-      <c r="J47" s="1">
-        <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="J47" s="12">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
       </c>
       <c r="K47" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M47" s="4">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="N47" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P47" s="1">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Q47" s="9">
-        <v>10532587</v>
+        <v>12260416</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="S47" s="1">
         <v>6</v>
@@ -27271,197 +27247,197 @@
     </row>
     <row r="48" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
-        <v>46238</v>
-      </c>
-      <c r="C48" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C48" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E48" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F48" s="9">
-        <v>12289497</v>
+        <v>12260416</v>
       </c>
       <c r="G48" s="1">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H48" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I48" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.11904761904761904</v>
-      </c>
-      <c r="J48" s="1">
-        <f t="shared" si="6"/>
-        <v>0.88095238095238093</v>
+        <v>0.2</v>
+      </c>
+      <c r="J48" s="12">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
       </c>
       <c r="K48" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.88095238095238093</v>
+        <v>0.8</v>
       </c>
       <c r="M48" s="4">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="N48" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P48" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="P48" s="1">
+        <v>400</v>
       </c>
       <c r="Q48" s="9">
-        <v>10532587</v>
+        <v>12260416</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="S48" s="1">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B49" s="4">
-        <v>46238</v>
-      </c>
-      <c r="C49" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C49" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E49" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F49" s="9">
-        <v>12289497</v>
+        <v>12260416</v>
       </c>
       <c r="G49" s="1">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I49" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
-      </c>
-      <c r="J49" s="1">
-        <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="J49" s="12">
+        <f t="shared" si="4"/>
+        <v>0.30769230769230771</v>
       </c>
       <c r="K49" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="M49" s="4">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="N49" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P49" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="P49" s="1">
+        <v>400</v>
       </c>
       <c r="Q49" s="9">
-        <v>10532587</v>
+        <v>12260416</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S49" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B50" s="4">
-        <v>46238</v>
-      </c>
-      <c r="C50" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C50" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E50" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F50" s="9">
-        <v>12289497</v>
+        <v>12260416</v>
       </c>
       <c r="G50" s="1">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H50" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I50" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
-      </c>
-      <c r="J50" s="1">
-        <f t="shared" si="6"/>
-        <v>1</v>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="J50" s="12">
+        <f t="shared" si="4"/>
+        <v>0.94736842105263164</v>
       </c>
       <c r="K50" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.94736842105263164</v>
       </c>
       <c r="M50" s="4">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="N50" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P50" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="P50" s="1">
+        <v>400</v>
       </c>
       <c r="Q50" s="9">
-        <v>10532587</v>
+        <v>12260416</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="S50" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B51" s="4">
-        <v>46238</v>
-      </c>
-      <c r="C51" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C51" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E51" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="F51" s="9">
-        <v>12289497</v>
+        <v>12260416</v>
       </c>
       <c r="G51" s="1">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
@@ -27470,8 +27446,8 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J51" s="1">
-        <f t="shared" si="6"/>
+      <c r="J51" s="12">
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K51" s="5">
@@ -27479,337 +27455,337 @@
         <v>1</v>
       </c>
       <c r="M51" s="4">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="N51" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P51" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q51" s="9">
+        <v>12260416</v>
+      </c>
+      <c r="R51" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O51" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q51" s="9">
-        <v>10532587</v>
-      </c>
-      <c r="R51" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="S51" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B52" s="4">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="C52" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E52" s="1">
-        <v>100</v>
-      </c>
       <c r="F52" s="9">
-        <v>10532587</v>
+        <v>12260416</v>
       </c>
       <c r="G52" s="1">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="H52" s="1">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="I52" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.25833333333333336</v>
+        <v>0.1875</v>
       </c>
       <c r="J52" s="12">
-        <f t="shared" ref="J52:J60" si="7">ABS(G$3-I52)</f>
-        <v>0.7416666666666667</v>
+        <f t="shared" si="4"/>
+        <v>0.8125</v>
       </c>
       <c r="K52" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.7416666666666667</v>
+        <v>0.8125</v>
       </c>
       <c r="M52" s="4">
-        <v>46239</v>
+        <v>46227</v>
       </c>
       <c r="N52" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P52" s="1">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="Q52" s="9">
-        <v>10532587</v>
+        <v>12260416</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="S52" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B53" s="4">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="C53" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E53" s="1">
-        <v>150</v>
+        <v>18</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F53" s="9">
-        <v>10532587</v>
+        <v>12260416</v>
       </c>
       <c r="G53" s="1">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="H53" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I53" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>8.5714285714285715E-2</v>
+        <v>0</v>
       </c>
       <c r="J53" s="12">
-        <f t="shared" si="7"/>
-        <v>0.91428571428571426</v>
+        <f>ABS(G$3-I53)</f>
+        <v>1</v>
       </c>
       <c r="K53" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.91428571428571426</v>
+        <v>1</v>
       </c>
       <c r="M53" s="4">
-        <v>46239</v>
+        <v>46227</v>
       </c>
       <c r="N53" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P53" s="1">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="Q53" s="9">
-        <v>10532587</v>
+        <v>12260416</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="S53" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B54" s="4">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="C54" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E54" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F54" s="9">
-        <v>10532587</v>
+        <v>12260415</v>
       </c>
       <c r="G54" s="1">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="H54" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I54" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.15238095238095239</v>
+        <v>0</v>
       </c>
       <c r="J54" s="12">
-        <f t="shared" si="7"/>
-        <v>0.84761904761904761</v>
+        <f t="shared" ref="J54:J61" si="5">ABS(G$3-I54)</f>
+        <v>1</v>
       </c>
       <c r="K54" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.84761904761904761</v>
+        <v>1</v>
       </c>
       <c r="M54" s="4">
-        <v>46239</v>
+        <v>46227</v>
       </c>
       <c r="N54" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P54" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P54" s="1">
-        <v>200</v>
-      </c>
       <c r="Q54" s="9">
-        <v>10532587</v>
+        <v>12260416</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="S54" s="1">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B55" s="4">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="C55" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E55" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F55" s="9">
-        <v>10532587</v>
+        <v>12260415</v>
       </c>
       <c r="G55" s="1">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="H55" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I55" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>5.9405940594059403E-2</v>
+        <v>0</v>
       </c>
       <c r="J55" s="12">
-        <f t="shared" si="7"/>
-        <v>0.94059405940594054</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="K55" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.94059405940594054</v>
+        <v>1</v>
       </c>
       <c r="M55" s="4">
-        <v>46237</v>
+        <v>46227</v>
       </c>
       <c r="N55" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P55" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P55" s="1">
-        <v>300</v>
-      </c>
       <c r="Q55" s="9">
-        <v>10532587</v>
+        <v>12260416</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="S55" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="C56" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="E56" s="1">
+        <v>300</v>
       </c>
       <c r="F56" s="9">
-        <v>10532587</v>
+        <v>12260415</v>
       </c>
       <c r="G56" s="1">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="H56" s="1">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="I56" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.7068965517241379</v>
+        <v>0</v>
       </c>
       <c r="J56" s="12">
-        <f t="shared" si="7"/>
-        <v>0.2931034482758621</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="K56" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.2931034482758621</v>
+        <v>1</v>
       </c>
       <c r="M56" s="4">
-        <v>46239</v>
+        <v>46227</v>
       </c>
       <c r="N56" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O56" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P56" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P56" s="1">
-        <v>300</v>
-      </c>
       <c r="Q56" s="9">
-        <v>10532587</v>
+        <v>12260416</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="S56" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B57" s="4">
-        <v>46237</v>
+        <v>46227</v>
       </c>
       <c r="C57" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E57" s="1">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="F57" s="9">
-        <v>10532587</v>
+        <v>12260415</v>
       </c>
       <c r="G57" s="1">
-        <v>174</v>
+        <v>19</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
@@ -27819,7 +27795,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K57" s="5">
@@ -27827,647 +27803,417 @@
         <v>1</v>
       </c>
       <c r="M57" s="4">
-        <v>46239</v>
+        <v>46227</v>
       </c>
       <c r="N57" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P57" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P57" s="1">
-        <v>300</v>
-      </c>
       <c r="Q57" s="9">
-        <v>10532587</v>
+        <v>12260416</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S57" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B58" s="4">
-        <v>46237</v>
+        <v>46227</v>
       </c>
       <c r="C58" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E58" s="1">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="F58" s="9">
-        <v>10532587</v>
+        <v>12260415</v>
       </c>
       <c r="G58" s="1">
-        <v>174</v>
+        <v>19</v>
       </c>
       <c r="H58" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I58" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.15789473684210525</v>
       </c>
       <c r="J58" s="12">
-        <f t="shared" si="7"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.84210526315789469</v>
       </c>
       <c r="K58" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.84210526315789469</v>
       </c>
       <c r="M58" s="4">
-        <v>46237</v>
+        <v>46220</v>
       </c>
       <c r="N58" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q58" s="9">
-        <v>10532587</v>
+        <v>12264714</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="S58" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B59" s="4">
-        <v>46237</v>
+        <v>46227</v>
       </c>
       <c r="C59" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E59" s="1">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="F59" s="9">
-        <v>10532587</v>
+        <v>12260415</v>
       </c>
       <c r="G59" s="1">
-        <v>174</v>
+        <v>18</v>
       </c>
       <c r="H59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>5.5555555555555552E-2</v>
       </c>
       <c r="J59" s="12">
-        <f t="shared" si="7"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.94444444444444442</v>
       </c>
       <c r="K59" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.94444444444444442</v>
       </c>
       <c r="M59" s="4">
-        <v>46237</v>
+        <v>46227</v>
       </c>
       <c r="N59" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P59" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="P59" s="1">
+        <v>600</v>
       </c>
       <c r="Q59" s="9">
-        <v>10532587</v>
+        <v>12260415</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="S59" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B60" s="4">
-        <v>46237</v>
+        <v>46227</v>
       </c>
       <c r="C60" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E60" s="1">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="F60" s="9">
-        <v>10532587</v>
+        <v>12260415</v>
       </c>
       <c r="G60" s="1">
-        <v>174</v>
+        <v>18</v>
       </c>
       <c r="H60" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I60" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>3.4482758620689655E-2</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="J60" s="12">
-        <f t="shared" si="7"/>
-        <v>0.96551724137931039</v>
+        <f t="shared" si="5"/>
+        <v>0.77777777777777779</v>
       </c>
       <c r="K60" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.96551724137931039</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="M60" s="4">
-        <v>46237</v>
+        <v>46227</v>
       </c>
       <c r="N60" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P60" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="P60" s="1">
+        <v>700</v>
       </c>
       <c r="Q60" s="9">
-        <v>10532587</v>
+        <v>12260415</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="S60" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
-        <v>46237</v>
+        <v>46227</v>
       </c>
       <c r="C61" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="E61" s="1">
+        <v>900</v>
       </c>
       <c r="F61" s="9">
-        <v>10532587</v>
+        <v>12260415</v>
       </c>
       <c r="G61" s="1">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="H61" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="J61" s="12">
-        <f>ABS(G$3-I61)</f>
-        <v>0.84</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="K61" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="M61" s="4">
-        <v>46237</v>
+        <v>46227</v>
       </c>
       <c r="N61" s="12">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P61" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="P61" s="1">
+        <v>800</v>
       </c>
       <c r="Q61" s="9">
-        <v>10532587</v>
+        <v>12260416</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="S61" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
-        <v>46239</v>
+        <v>46227</v>
       </c>
       <c r="C62" s="12">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D62" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E62" s="1">
-        <v>100</v>
-      </c>
       <c r="F62" s="9">
-        <v>10532587</v>
+        <v>12260415</v>
       </c>
       <c r="G62" s="1">
-        <v>219</v>
+        <v>40</v>
       </c>
       <c r="H62" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>6.3926940639269403E-2</v>
+        <v>0</v>
       </c>
       <c r="J62" s="12">
-        <f t="shared" ref="J62:J67" si="8">ABS(G$3-I62)</f>
-        <v>0.9360730593607306</v>
+        <f t="shared" ref="J62" si="6">ABS(G$3-I62)</f>
+        <v>1</v>
       </c>
       <c r="K62" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.9360730593607306</v>
-      </c>
-      <c r="M62" s="4">
-        <v>46237</v>
-      </c>
-      <c r="N62" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
-      </c>
-      <c r="O62" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P62" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q62" s="9">
-        <v>10532587</v>
-      </c>
-      <c r="R62" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="S62" s="1">
         <v>1</v>
       </c>
+      <c r="M62" s="4"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B63" s="4">
-        <v>46239</v>
-      </c>
-      <c r="C63" s="12">
-        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E63" s="1">
-        <v>150</v>
-      </c>
-      <c r="F63" s="9">
-        <v>10532587</v>
-      </c>
-      <c r="G63" s="1">
-        <v>219</v>
-      </c>
-      <c r="H63" s="1">
-        <v>0</v>
-      </c>
-      <c r="I63" s="3">
-        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
-      </c>
-      <c r="J63" s="12">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="K63" s="5">
-        <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
-      </c>
-      <c r="M63" s="4">
-        <v>46237</v>
-      </c>
-      <c r="N63" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P63" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q63" s="9">
-        <v>10532587</v>
-      </c>
-      <c r="R63" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="S63" s="1">
-        <v>1</v>
-      </c>
+      <c r="B63" s="4"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="5"/>
+      <c r="M63" s="4"/>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B64" s="4">
-        <v>46239</v>
-      </c>
-      <c r="C64" s="12">
-        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E64" s="1">
-        <v>200</v>
-      </c>
-      <c r="F64" s="9">
-        <v>10532587</v>
-      </c>
-      <c r="G64" s="1">
-        <v>216</v>
-      </c>
-      <c r="H64" s="1">
-        <v>18</v>
-      </c>
-      <c r="I64" s="3">
-        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="J64" s="12">
-        <f t="shared" si="8"/>
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="K64" s="5">
-        <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="M64" s="4">
-        <v>46239</v>
-      </c>
-      <c r="N64" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
-      </c>
-      <c r="O64" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P64" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q64" s="9">
-        <v>10532587</v>
-      </c>
-      <c r="R64" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S64" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B65" s="4">
-        <v>46239</v>
-      </c>
-      <c r="C65" s="12">
-        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E65" s="1">
-        <v>300</v>
-      </c>
-      <c r="F65" s="9">
-        <v>10532587</v>
-      </c>
-      <c r="G65" s="1">
-        <v>210</v>
-      </c>
-      <c r="H65" s="1">
-        <v>8</v>
-      </c>
-      <c r="I65" s="3">
-        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>3.8095238095238099E-2</v>
-      </c>
-      <c r="J65" s="12">
-        <f t="shared" si="8"/>
-        <v>0.96190476190476193</v>
-      </c>
-      <c r="K65" s="5">
-        <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.96190476190476193</v>
-      </c>
-      <c r="M65" s="4">
-        <v>46239</v>
-      </c>
-      <c r="N65" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
-      </c>
-      <c r="O65" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P65" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q65" s="9">
-        <v>10532587</v>
-      </c>
-      <c r="R65" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S65" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B66" s="4">
-        <v>46239</v>
-      </c>
-      <c r="C66" s="12">
-        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>32</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F66" s="9">
-        <v>10532587</v>
-      </c>
-      <c r="G66" s="1">
-        <v>187</v>
-      </c>
-      <c r="H66" s="1">
-        <v>24</v>
-      </c>
-      <c r="I66" s="3">
-        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.12834224598930483</v>
-      </c>
-      <c r="J66" s="12">
-        <f t="shared" si="8"/>
-        <v>0.87165775401069512</v>
-      </c>
-      <c r="K66" s="5">
-        <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.87165775401069512</v>
-      </c>
-      <c r="M66" s="4">
-        <v>46239</v>
-      </c>
-      <c r="N66" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>32</v>
-      </c>
-      <c r="O66" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P66" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q66" s="9">
-        <v>10532587</v>
-      </c>
-      <c r="R66" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="S66" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B64" s="4"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="5"/>
+      <c r="M64" s="4"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B65" s="4"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="5"/>
+      <c r="M65" s="4"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B66" s="4"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="5"/>
+      <c r="M66" s="4"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B67" s="4"/>
-      <c r="C67" s="12"/>
-      <c r="F67" s="9"/>
       <c r="I67" s="3"/>
-      <c r="J67" s="12"/>
+      <c r="J67" s="1"/>
       <c r="K67" s="5"/>
       <c r="M67" s="4"/>
     </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B68" s="4"/>
-      <c r="G68" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="I68" s="3"/>
       <c r="J68" s="1"/>
       <c r="K68" s="5"/>
       <c r="M68" s="4"/>
     </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B69" s="4"/>
       <c r="I69" s="3"/>
       <c r="J69" s="1"/>
       <c r="K69" s="5"/>
       <c r="M69" s="4"/>
     </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B70" s="4"/>
       <c r="I70" s="3"/>
       <c r="J70" s="1"/>
       <c r="K70" s="5"/>
       <c r="M70" s="4"/>
     </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B71" s="4"/>
       <c r="I71" s="3"/>
       <c r="J71" s="1"/>
       <c r="K71" s="5"/>
       <c r="M71" s="4"/>
     </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B72" s="4"/>
       <c r="I72" s="3"/>
       <c r="J72" s="1"/>
       <c r="K72" s="5"/>
       <c r="M72" s="4"/>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B73" s="4"/>
       <c r="I73" s="3"/>
       <c r="J73" s="1"/>
       <c r="K73" s="5"/>
       <c r="M73" s="4"/>
     </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B74" s="4"/>
       <c r="I74" s="3"/>
       <c r="J74" s="1"/>
       <c r="K74" s="5"/>
       <c r="M74" s="4"/>
     </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B75" s="4"/>
       <c r="I75" s="3"/>
       <c r="J75" s="1"/>
       <c r="K75" s="5"/>
       <c r="M75" s="4"/>
     </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B76" s="4"/>
       <c r="I76" s="3"/>
       <c r="J76" s="1"/>
       <c r="K76" s="5"/>
       <c r="M76" s="4"/>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B77" s="4"/>
       <c r="I77" s="3"/>
       <c r="J77" s="1"/>
       <c r="K77" s="5"/>
       <c r="M77" s="4"/>
     </row>
-    <row r="78" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B78" s="4"/>
       <c r="I78" s="3"/>
       <c r="J78" s="1"/>
       <c r="K78" s="5"/>
       <c r="M78" s="4"/>
     </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B79" s="4"/>
       <c r="I79" s="3"/>
       <c r="J79" s="1"/>
       <c r="K79" s="5"/>
       <c r="M79" s="4"/>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B80" s="4"/>
       <c r="I80" s="3"/>
       <c r="J80" s="1"/>
@@ -29446,8 +29192,6 @@
       <c r="J219" s="1"/>
       <c r="K219" s="5"/>
       <c r="M219" s="4"/>
-      <c r="U219" s="1"/>
-      <c r="V219" s="1"/>
     </row>
     <row r="220" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B220" s="4"/>
@@ -29455,8 +29199,6 @@
       <c r="J220" s="1"/>
       <c r="K220" s="5"/>
       <c r="M220" s="4"/>
-      <c r="U220" s="1"/>
-      <c r="V220" s="1"/>
     </row>
     <row r="221" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B221" s="4"/>
@@ -29464,6 +29206,8 @@
       <c r="J221" s="1"/>
       <c r="K221" s="5"/>
       <c r="M221" s="4"/>
+      <c r="U221" s="1"/>
+      <c r="V221" s="1"/>
     </row>
     <row r="222" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B222" s="4"/>
@@ -29471,6 +29215,8 @@
       <c r="J222" s="1"/>
       <c r="K222" s="5"/>
       <c r="M222" s="4"/>
+      <c r="U222" s="1"/>
+      <c r="V222" s="1"/>
     </row>
     <row r="223" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B223" s="4"/>
@@ -29568,14 +29314,14 @@
       <c r="I236" s="3"/>
       <c r="J236" s="1"/>
       <c r="K236" s="5"/>
-      <c r="M236" s="8"/>
+      <c r="M236" s="4"/>
     </row>
     <row r="237" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B237" s="4"/>
       <c r="I237" s="3"/>
       <c r="J237" s="1"/>
       <c r="K237" s="5"/>
-      <c r="M237" s="8"/>
+      <c r="M237" s="4"/>
     </row>
     <row r="238" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B238" s="4"/>
@@ -29589,14 +29335,14 @@
       <c r="I239" s="3"/>
       <c r="J239" s="1"/>
       <c r="K239" s="5"/>
-      <c r="M239" s="4"/>
+      <c r="M239" s="8"/>
     </row>
     <row r="240" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B240" s="4"/>
       <c r="I240" s="3"/>
       <c r="J240" s="1"/>
       <c r="K240" s="5"/>
-      <c r="M240" s="4"/>
+      <c r="M240" s="8"/>
     </row>
     <row r="241" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B241" s="4"/>
@@ -29875,12 +29621,14 @@
       <c r="B280" s="4"/>
       <c r="I280" s="3"/>
       <c r="J280" s="1"/>
+      <c r="K280" s="5"/>
       <c r="M280" s="4"/>
     </row>
     <row r="281" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B281" s="4"/>
       <c r="I281" s="3"/>
       <c r="J281" s="1"/>
+      <c r="K281" s="5"/>
       <c r="M281" s="4"/>
     </row>
     <row r="282" spans="2:13" x14ac:dyDescent="0.3">
@@ -29899,11 +29647,13 @@
       <c r="B284" s="4"/>
       <c r="I284" s="3"/>
       <c r="J284" s="1"/>
+      <c r="M284" s="4"/>
     </row>
     <row r="285" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B285" s="4"/>
       <c r="I285" s="3"/>
       <c r="J285" s="1"/>
+      <c r="M285" s="4"/>
     </row>
     <row r="286" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B286" s="4"/>
@@ -29986,9 +29736,6 @@
       <c r="J301" s="1"/>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A302" t="s">
-        <v>0</v>
-      </c>
       <c r="B302" s="4"/>
       <c r="I302" s="3"/>
       <c r="J302" s="1"/>
@@ -29999,6 +29746,9 @@
       <c r="J303" s="1"/>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>0</v>
+      </c>
       <c r="B304" s="4"/>
       <c r="I304" s="3"/>
       <c r="J304" s="1"/>
@@ -30189,9 +29939,6 @@
       <c r="J341" s="1"/>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A342" t="s">
-        <v>0</v>
-      </c>
       <c r="B342" s="4"/>
       <c r="I342" s="3"/>
       <c r="J342" s="1"/>
@@ -30202,6 +29949,9 @@
       <c r="J343" s="1"/>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>0</v>
+      </c>
       <c r="B344" s="4"/>
       <c r="I344" s="3"/>
       <c r="J344" s="1"/>
@@ -30615,17 +30365,11 @@
       <c r="B426" s="4"/>
       <c r="I426" s="3"/>
       <c r="J426" s="1"/>
-      <c r="M426" s="7"/>
-      <c r="N426" s="7"/>
-      <c r="O426" s="7"/>
     </row>
     <row r="427" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B427" s="4"/>
       <c r="I427" s="3"/>
       <c r="J427" s="1"/>
-      <c r="M427" s="7"/>
-      <c r="N427" s="7"/>
-      <c r="O427" s="7"/>
     </row>
     <row r="428" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B428" s="4"/>
@@ -30768,7 +30512,7 @@
       <c r="I445" s="3"/>
       <c r="J445" s="1"/>
       <c r="M445" s="7"/>
-      <c r="N445" s="8"/>
+      <c r="N445" s="7"/>
       <c r="O445" s="7"/>
     </row>
     <row r="446" spans="2:15" x14ac:dyDescent="0.3">
@@ -30784,7 +30528,7 @@
       <c r="I447" s="3"/>
       <c r="J447" s="1"/>
       <c r="M447" s="7"/>
-      <c r="N447" s="7"/>
+      <c r="N447" s="8"/>
       <c r="O447" s="7"/>
     </row>
     <row r="448" spans="2:15" x14ac:dyDescent="0.3">
@@ -30999,11 +30743,17 @@
       <c r="B474" s="4"/>
       <c r="I474" s="3"/>
       <c r="J474" s="1"/>
+      <c r="M474" s="7"/>
+      <c r="N474" s="7"/>
+      <c r="O474" s="7"/>
     </row>
     <row r="475" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B475" s="4"/>
       <c r="I475" s="3"/>
       <c r="J475" s="1"/>
+      <c r="M475" s="7"/>
+      <c r="N475" s="7"/>
+      <c r="O475" s="7"/>
     </row>
     <row r="476" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B476" s="4"/>
@@ -32031,9 +31781,6 @@
       <c r="J680" s="1"/>
     </row>
     <row r="681" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A681" t="s">
-        <v>0</v>
-      </c>
       <c r="B681" s="4"/>
       <c r="I681" s="3"/>
       <c r="J681" s="1"/>
@@ -32044,6 +31791,9 @@
       <c r="J682" s="1"/>
     </row>
     <row r="683" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A683" t="s">
+        <v>0</v>
+      </c>
       <c r="B683" s="4"/>
       <c r="I683" s="3"/>
       <c r="J683" s="1"/>
@@ -32064,9 +31814,6 @@
       <c r="J686" s="1"/>
     </row>
     <row r="687" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A687" t="s">
-        <v>0</v>
-      </c>
       <c r="B687" s="4"/>
       <c r="I687" s="3"/>
       <c r="J687" s="1"/>
@@ -32077,6 +31824,9 @@
       <c r="J688" s="1"/>
     </row>
     <row r="689" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A689" t="s">
+        <v>0</v>
+      </c>
       <c r="B689" s="4"/>
       <c r="I689" s="3"/>
       <c r="J689" s="1"/>
@@ -32097,9 +31847,6 @@
       <c r="J692" s="1"/>
     </row>
     <row r="693" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A693" t="s">
-        <v>0</v>
-      </c>
       <c r="B693" s="4"/>
       <c r="I693" s="3"/>
       <c r="J693" s="1"/>
@@ -32110,6 +31857,9 @@
       <c r="J694" s="1"/>
     </row>
     <row r="695" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A695" t="s">
+        <v>0</v>
+      </c>
       <c r="B695" s="4"/>
       <c r="I695" s="3"/>
       <c r="J695" s="1"/>
@@ -32130,9 +31880,6 @@
       <c r="J698" s="1"/>
     </row>
     <row r="699" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A699" t="s">
-        <v>0</v>
-      </c>
       <c r="B699" s="4"/>
       <c r="I699" s="3"/>
       <c r="J699" s="1"/>
@@ -32143,6 +31890,9 @@
       <c r="J700" s="1"/>
     </row>
     <row r="701" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A701" t="s">
+        <v>0</v>
+      </c>
       <c r="B701" s="4"/>
       <c r="I701" s="3"/>
       <c r="J701" s="1"/>
@@ -32163,9 +31913,6 @@
       <c r="J704" s="1"/>
     </row>
     <row r="705" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A705" t="s">
-        <v>0</v>
-      </c>
       <c r="B705" s="4"/>
       <c r="I705" s="3"/>
       <c r="J705" s="1"/>
@@ -32176,6 +31923,9 @@
       <c r="J706" s="1"/>
     </row>
     <row r="707" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A707" t="s">
+        <v>0</v>
+      </c>
       <c r="B707" s="4"/>
       <c r="I707" s="3"/>
       <c r="J707" s="1"/>
@@ -32196,9 +31946,6 @@
       <c r="J710" s="1"/>
     </row>
     <row r="711" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A711" t="s">
-        <v>0</v>
-      </c>
       <c r="B711" s="4"/>
       <c r="I711" s="3"/>
       <c r="J711" s="1"/>
@@ -32209,6 +31956,9 @@
       <c r="J712" s="1"/>
     </row>
     <row r="713" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A713" t="s">
+        <v>0</v>
+      </c>
       <c r="B713" s="4"/>
       <c r="I713" s="3"/>
       <c r="J713" s="1"/>
@@ -32248,173 +31998,170 @@
       <c r="I720" s="3"/>
       <c r="J720" s="1"/>
     </row>
-    <row r="721" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="721" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B721" s="4"/>
       <c r="I721" s="3"/>
       <c r="J721" s="1"/>
     </row>
-    <row r="722" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="722" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B722" s="4"/>
       <c r="I722" s="3"/>
       <c r="J722" s="1"/>
     </row>
-    <row r="723" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="723" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B723" s="4"/>
       <c r="I723" s="3"/>
       <c r="J723" s="1"/>
     </row>
-    <row r="724" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="724" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B724" s="4"/>
       <c r="I724" s="3"/>
       <c r="J724" s="1"/>
     </row>
-    <row r="725" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="725" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B725" s="4"/>
       <c r="I725" s="3"/>
       <c r="J725" s="1"/>
     </row>
-    <row r="726" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="726" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B726" s="4"/>
       <c r="I726" s="3"/>
       <c r="J726" s="1"/>
     </row>
-    <row r="727" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="727" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B727" s="4"/>
       <c r="I727" s="3"/>
       <c r="J727" s="1"/>
     </row>
-    <row r="728" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="728" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B728" s="4"/>
       <c r="I728" s="3"/>
       <c r="J728" s="1"/>
     </row>
-    <row r="729" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="729" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B729" s="4"/>
       <c r="I729" s="3"/>
       <c r="J729" s="1"/>
     </row>
-    <row r="730" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="730" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B730" s="4"/>
       <c r="I730" s="3"/>
       <c r="J730" s="1"/>
     </row>
-    <row r="731" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="731" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B731" s="4"/>
       <c r="I731" s="3"/>
       <c r="J731" s="1"/>
     </row>
-    <row r="732" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="732" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B732" s="4"/>
       <c r="I732" s="3"/>
       <c r="J732" s="1"/>
     </row>
-    <row r="733" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="733" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B733" s="4"/>
       <c r="I733" s="3"/>
       <c r="J733" s="1"/>
     </row>
-    <row r="734" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="734" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B734" s="4"/>
       <c r="I734" s="3"/>
       <c r="J734" s="1"/>
     </row>
-    <row r="735" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A735" t="s">
-        <v>0</v>
-      </c>
+    <row r="735" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B735" s="4"/>
       <c r="I735" s="3"/>
       <c r="J735" s="1"/>
     </row>
-    <row r="736" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="736" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B736" s="4"/>
       <c r="I736" s="3"/>
       <c r="J736" s="1"/>
     </row>
-    <row r="737" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A737" t="s">
+        <v>0</v>
+      </c>
       <c r="B737" s="4"/>
       <c r="I737" s="3"/>
       <c r="J737" s="1"/>
     </row>
-    <row r="738" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B738" s="4"/>
       <c r="I738" s="3"/>
       <c r="J738" s="1"/>
     </row>
-    <row r="739" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B739" s="4"/>
       <c r="I739" s="3"/>
       <c r="J739" s="1"/>
     </row>
-    <row r="740" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B740" s="4"/>
       <c r="I740" s="3"/>
       <c r="J740" s="1"/>
     </row>
-    <row r="741" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B741" s="4"/>
       <c r="I741" s="3"/>
       <c r="J741" s="1"/>
     </row>
-    <row r="742" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B742" s="4"/>
       <c r="I742" s="3"/>
       <c r="J742" s="1"/>
     </row>
-    <row r="743" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B743" s="4"/>
       <c r="I743" s="3"/>
       <c r="J743" s="1"/>
     </row>
-    <row r="744" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B744" s="4"/>
       <c r="I744" s="3"/>
       <c r="J744" s="1"/>
     </row>
-    <row r="745" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B745" s="4"/>
       <c r="I745" s="3"/>
       <c r="J745" s="1"/>
     </row>
-    <row r="746" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B746" s="4"/>
       <c r="I746" s="3"/>
       <c r="J746" s="1"/>
     </row>
-    <row r="747" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B747" s="4"/>
       <c r="I747" s="3"/>
       <c r="J747" s="1"/>
     </row>
-    <row r="748" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B748" s="4"/>
       <c r="I748" s="3"/>
       <c r="J748" s="1"/>
     </row>
-    <row r="749" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B749" s="4"/>
       <c r="I749" s="3"/>
       <c r="J749" s="1"/>
     </row>
-    <row r="750" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B750" s="4"/>
       <c r="I750" s="3"/>
       <c r="J750" s="1"/>
     </row>
-    <row r="751" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B751" s="4"/>
       <c r="I751" s="3"/>
       <c r="J751" s="1"/>
     </row>
-    <row r="752" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B752" s="4"/>
       <c r="I752" s="3"/>
       <c r="J752" s="1"/>
     </row>
     <row r="753" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A753" t="s">
-        <v>0</v>
-      </c>
       <c r="B753" s="4"/>
       <c r="I753" s="3"/>
       <c r="J753" s="1"/>
@@ -32425,6 +32172,9 @@
       <c r="J754" s="1"/>
     </row>
     <row r="755" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A755" t="s">
+        <v>0</v>
+      </c>
       <c r="B755" s="4"/>
       <c r="I755" s="3"/>
       <c r="J755" s="1"/>
@@ -32595,6 +32345,7 @@
       <c r="J788" s="1"/>
     </row>
     <row r="789" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B789" s="4"/>
       <c r="I789" s="3"/>
       <c r="J789" s="1"/>
     </row>
@@ -32604,7 +32355,6 @@
       <c r="J790" s="1"/>
     </row>
     <row r="791" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B791" s="4"/>
       <c r="I791" s="3"/>
       <c r="J791" s="1"/>
     </row>
@@ -32655,7 +32405,6 @@
     </row>
     <row r="801" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B801" s="4"/>
-      <c r="G801" s="4"/>
       <c r="I801" s="3"/>
       <c r="J801" s="1"/>
     </row>
@@ -32666,6 +32415,7 @@
     </row>
     <row r="803" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B803" s="4"/>
+      <c r="G803" s="4"/>
       <c r="I803" s="3"/>
       <c r="J803" s="1"/>
     </row>
@@ -32793,6 +32543,16 @@
       <c r="B828" s="4"/>
       <c r="I828" s="3"/>
       <c r="J828" s="1"/>
+    </row>
+    <row r="829" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B829" s="4"/>
+      <c r="I829" s="3"/>
+      <c r="J829" s="1"/>
+    </row>
+    <row r="830" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B830" s="4"/>
+      <c r="I830" s="3"/>
+      <c r="J830" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\4_NX5a\09_Information\10_FTQ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\5_MB MMA\09_Information\10_FTQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81C1498-AB3E-42BA-9099-F89FB4C26158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234EDC18-20D9-4775-80C6-E7B7E0CD7EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
   </bookViews>
   <sheets>
-    <sheet name="BASE DE DATOS RIVIAN" sheetId="1" r:id="rId1"/>
+    <sheet name="BASE DE DATOS" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS RIVIAN'!$B$4:$J$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$67</definedName>
     <definedName name="DATA_01">[1]Data_Lineal!$H$4:$Y$30</definedName>
     <definedName name="DB_01">#REF!</definedName>
     <definedName name="DB_CAP01">'[2]CAPACIDAD (1)'!$X$9:$AM$29</definedName>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="62">
   <si>
     <t>*</t>
   </si>
@@ -111,112 +111,145 @@
     <t>PRODUCCIÓN</t>
   </si>
   <si>
-    <t>1100A</t>
+    <t>SCR MMA</t>
   </si>
   <si>
-    <t>Falso rechazo Op.1100A</t>
+    <t>EOL</t>
   </si>
   <si>
-    <t>1100B</t>
+    <t>Mal enrollado de cables Op.200</t>
   </si>
   <si>
-    <t>Hyundai/KIA</t>
+    <t>Mal ensamble con cable AB dañado Op.150</t>
   </si>
   <si>
-    <t>Falta de puntos de grasa Op.100</t>
+    <t>Mala colocación de cable AB en doblez Op.150</t>
   </si>
   <si>
-    <t>Corredera mal posicionada Op.400</t>
+    <t>Cables dañados por doblez Op.150</t>
   </si>
   <si>
-    <t>Corto de soldadura Op.800</t>
+    <t>Falla en inspección visual no detecta piezas NOK Op.200</t>
   </si>
   <si>
-    <t>Falta de soldadura Op.800</t>
+    <t>Latch y Resorte no llegan a posición correcta Op.300</t>
   </si>
   <si>
-    <t>Falta de soldadura Op.1100A</t>
+    <t>Falla 3320.041 Op.EOL</t>
   </si>
   <si>
-    <t>Lever Barcode Scan Facture Op.300</t>
+    <t>Falla 3310.011 Op.EOL</t>
   </si>
   <si>
-    <t>Falla en lectura de Scanner Op.300</t>
+    <t>Falsos rechazos Op.EOL</t>
   </si>
   <si>
-    <t>Falla de inspección visual Op.200</t>
+    <t>Falla 3550.002 Op.EOL</t>
   </si>
   <si>
-    <t>Falla de inspección visual Op.300</t>
+    <t>Falla 6000.001 Op.EOL</t>
   </si>
   <si>
-    <t>Falla de inspección visual Op.600</t>
+    <t>Falla 2110.020 Op.EOL</t>
   </si>
   <si>
-    <t>Falla de inspección visual Op.400</t>
+    <t>Cable and Mark NG (Ventanita) Op.EOL</t>
   </si>
   <si>
-    <t>Falla en lectura de Scanner Op.400</t>
+    <t>SCCM MMA</t>
   </si>
   <si>
-    <t>Falla en atornillado Op.700</t>
+    <t>Falla de inspección visual en curvas sin NG Op.100</t>
   </si>
   <si>
-    <t>Falla sin especificación Op.900</t>
+    <t>Falla por falta de caída de SAS por gravedad sin NG Op.200</t>
   </si>
   <si>
-    <t>Mal embobinado en spiral Op.1100A</t>
+    <t>Dispensado de Grasa No Uniforme en Engrane sin NG Op.200</t>
   </si>
   <si>
-    <t>Falla de sensor de slai Op.400</t>
+    <t>Sensor no detecta mesa giratoria Op.400</t>
   </si>
   <si>
-    <t>Falla de sensor S$9 Op.400</t>
+    <t>Falla en inspección visual de Ruteo de Arnes Op.700</t>
   </si>
   <si>
-    <t>Material Towerdid Op.400</t>
+    <t>Falla en alimentador de Tornillos Op.800</t>
   </si>
   <si>
-    <t xml:space="preserve">SFC 965827AGG00003 is not in queue at operation Op.400 </t>
+    <t>Falla de inspección visual en Mordaza Métalica sin NG Op.100</t>
   </si>
   <si>
-    <t>Sin especificar Op. 600</t>
+    <t>Falla de Etiqueta por Guarda sin NG Op.300</t>
   </si>
   <si>
-    <t>Sin especificar ok Op. 600</t>
+    <t>Falla de inspección visual  Op.600</t>
   </si>
   <si>
-    <t>Falso Rechazo (version de SCR) Op.700</t>
+    <t>Inspección visual  no detecta PCB sin conector Op.600</t>
   </si>
   <si>
-    <t>Falta de grasa en PCB Op.400</t>
+    <t>Falla de inspección visual  Op.700</t>
   </si>
   <si>
-    <t>Detecta piezas de sobre-producción Op.400</t>
+    <t>No pide Inspección visual  del SCAS Op.700</t>
   </si>
   <si>
-    <t>Mezcla de material con index incorrecto Op.700</t>
+    <t>Mal enclipsado de Engrane en Housing (SAS) Op.200</t>
   </si>
   <si>
-    <t>Falla 0090.040 Op.1100A</t>
+    <t>Falla de Robot de enclipsado de Engrane en Housing (SAS) Op.200</t>
   </si>
   <si>
-    <t>Falla  0040.074 Op.1100A</t>
+    <t>Falla Mécanica en nido giratorio Op.500</t>
   </si>
   <si>
-    <t>Falla 0400.020 Op.1100A</t>
+    <t>Falla de inspección visual en Stator Housing Op.100</t>
   </si>
   <si>
-    <t>Falla 0400.030 Op.1100A</t>
+    <t>Falla de inspección visual en Rotor Housing Op.100</t>
   </si>
   <si>
-    <t>Falla 0060.005 Op.1100A</t>
+    <t>Falla de altura de cable AB Op.200</t>
   </si>
   <si>
-    <t>Falla 0090.004 Op.1100B</t>
+    <t>Cable Dummy dañado Op.200</t>
   </si>
   <si>
-    <t>Detecta pieza sin pasar en operación anterior Op.700</t>
+    <t>Falla "Codigo de barra no corresponde a la versión"  sin NOK Op.300</t>
+  </si>
+  <si>
+    <t>Falla 3110.004 Op.EOL</t>
+  </si>
+  <si>
+    <t>Falla 2270.004 Op.EOL</t>
+  </si>
+  <si>
+    <t>Falla de inspección visual no permite colocar Bearing Ring Op.100</t>
+  </si>
+  <si>
+    <t>Falla 2110.010 Op.EOL</t>
+  </si>
+  <si>
+    <t>Falla 2230.011 Op.EOL</t>
+  </si>
+  <si>
+    <t>Falla 3310.251 Op.EOL</t>
+  </si>
+  <si>
+    <t>Falla 3121.022 Op.EOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Safe launch</t>
+  </si>
+  <si>
+    <t>Palanca rayada</t>
+  </si>
+  <si>
+    <t>Pines desalineados</t>
   </si>
 </sst>
 </file>
@@ -298,7 +331,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -333,9 +366,22 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -24321,7 +24367,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K62" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K67" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CDAA4D20-2955-41E2-BD7E-9330E166FFF4}" name="Fecha" dataDxfId="18"/>
     <tableColumn id="9" xr3:uid="{F70BB124-92DE-4024-874C-EE3BA966CDE6}" name="Semana" dataDxfId="17">
@@ -24347,7 +24393,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S61" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S68" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D688BA2E-A64E-4433-85E0-7EDBF854AF60}" name="Fecha" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{D3EA5E8D-DD68-48AC-8DAC-4A4077839479}" name="Semana" dataDxfId="5">
@@ -24626,7 +24672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A1B645-8848-474A-88BA-FA9209B01B4F}">
-  <dimension ref="A1:V830"/>
+  <dimension ref="A1:V828"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
@@ -24636,7 +24682,7 @@
     <col min="6" max="7" width="11.5546875" style="1"/>
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="0" style="2" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" style="2" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="11.5546875" style="2"/>
     <col min="12" max="12" width="2.44140625" customWidth="1"/>
     <col min="13" max="13" width="13.88671875" style="1" customWidth="1"/>
@@ -24644,7 +24690,7 @@
     <col min="15" max="15" width="12.44140625" style="1" customWidth="1"/>
     <col min="16" max="16" width="13.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="50.44140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="56.109375" style="1" customWidth="1"/>
     <col min="19" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -24753,115 +24799,115 @@
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B5" s="4">
-        <v>46217</v>
+        <v>46224</v>
       </c>
       <c r="C5" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E5" s="1">
         <v>100</v>
       </c>
       <c r="F5" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G5" s="1">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="H5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>9.6153846153846159E-3</v>
+        <v>0</v>
       </c>
       <c r="J5" s="1">
-        <f t="shared" ref="J5:J13" si="0">ABS(G$3-I5)</f>
-        <v>0.99038461538461542</v>
+        <f t="shared" ref="J5:J9" si="0">ABS(G$3-I5)</f>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.99038461538461542</v>
+        <v>1</v>
       </c>
       <c r="M5" s="4">
-        <v>46217</v>
+        <v>46224</v>
       </c>
       <c r="N5" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P5" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q5" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="S5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B6" s="4">
-        <v>46217</v>
+        <v>46224</v>
       </c>
       <c r="C6" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F6" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G6" s="1">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c r="H6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>9.433962264150943E-3</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1">
         <f t="shared" si="0"/>
-        <v>0.99056603773584906</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.99056603773584906</v>
+        <v>1</v>
       </c>
       <c r="M6" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N6" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P6" s="1">
+        <v>150</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="P6" s="1">
-        <v>200</v>
-      </c>
-      <c r="Q6" s="9">
-        <v>12264732</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="S6" s="1">
         <v>1</v>
@@ -24869,344 +24915,344 @@
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
-        <v>46217</v>
+        <v>46224</v>
       </c>
       <c r="C7" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F7" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G7" s="1">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="H7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>2.6785714285714284E-2</v>
+        <v>0.11764705882352941</v>
       </c>
       <c r="J7" s="1">
         <f t="shared" si="0"/>
-        <v>0.9732142857142857</v>
+        <v>0.88235294117647056</v>
       </c>
       <c r="K7" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.9732142857142857</v>
+        <v>0.88235294117647056</v>
       </c>
       <c r="M7" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N7" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P7" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="Q7" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="S7" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
-        <v>46217</v>
+        <v>46224</v>
       </c>
       <c r="C8" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E8" s="1">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F8" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G8" s="1">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="H8" s="1">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.84042553191489366</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1">
         <f t="shared" si="0"/>
-        <v>0.15957446808510634</v>
+        <v>1</v>
       </c>
       <c r="K8" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.15957446808510634</v>
+        <v>1</v>
       </c>
       <c r="M8" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N8" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P8" s="1">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="Q8" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="S8" s="1">
-        <v>79</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="C9" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F9" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G9" s="1">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="H9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>1.0309278350515464E-2</v>
+        <v>0</v>
       </c>
       <c r="J9" s="1">
         <f t="shared" si="0"/>
-        <v>0.98969072164948457</v>
+        <v>1</v>
       </c>
       <c r="K9" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.98969072164948457</v>
+        <v>1</v>
       </c>
       <c r="M9" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N9" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P9" s="1">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="Q9" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="S9" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="C10" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="F10" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G10" s="1">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I10" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.12676056338028169</v>
       </c>
       <c r="J10" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" ref="J10:J12" si="1">ABS(G$3-I10)</f>
+        <v>0.87323943661971826</v>
       </c>
       <c r="K10" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.87323943661971826</v>
       </c>
       <c r="M10" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N10" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P10" s="1">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="Q10" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="S10" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="C11" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E11" s="1">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="F11" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G11" s="1">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="H11" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I11" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.12244897959183673</v>
+        <v>5.9701492537313432E-2</v>
       </c>
       <c r="J11" s="1">
-        <f t="shared" si="0"/>
-        <v>0.87755102040816324</v>
+        <f t="shared" si="1"/>
+        <v>0.94029850746268662</v>
       </c>
       <c r="K11" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.87755102040816324</v>
+        <v>0.94029850746268662</v>
       </c>
       <c r="M11" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N11" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P11" s="1">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="Q11" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>22</v>
       </c>
       <c r="S11" s="1">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="C12" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E12" s="1">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="F12" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G12" s="1">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I12" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.78260869565217395</v>
       </c>
       <c r="J12" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.21739130434782605</v>
       </c>
       <c r="K12" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.21739130434782605</v>
       </c>
       <c r="M12" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N12" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q12" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>23</v>
@@ -25217,57 +25263,57 @@
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="C13" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G13" s="1">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="H13" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I13" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>3.896103896103896E-2</v>
+        <v>0.2391304347826087</v>
       </c>
       <c r="J13" s="1">
-        <f t="shared" si="0"/>
-        <v>0.96103896103896103</v>
+        <f>ABS(G$3-I13)</f>
+        <v>0.76086956521739135</v>
       </c>
       <c r="K13" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.96103896103896103</v>
+        <v>0.76086956521739135</v>
       </c>
       <c r="M13" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N13" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q13" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="S13" s="1">
         <v>1</v>
@@ -25275,23 +25321,23 @@
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B14" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="C14" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E14" s="1">
         <v>100</v>
       </c>
       <c r="F14" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G14" s="1">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="H14" s="1">
         <v>0</v>
@@ -25301,7 +25347,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <f t="shared" ref="J14:J22" si="1">ABS(G$3-I14)</f>
+        <f t="shared" ref="J14:J24" si="2">ABS(G$3-I14)</f>
         <v>1</v>
       </c>
       <c r="K14" s="5">
@@ -25309,511 +25355,511 @@
         <v>1</v>
       </c>
       <c r="M14" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N14" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q14" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="S14" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="C15" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E15" s="1">
         <v>200</v>
       </c>
       <c r="F15" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G15" s="1">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="H15" s="1">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I15" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>4.9180327868852458E-2</v>
+        <v>0.4</v>
       </c>
       <c r="J15" s="1">
-        <f t="shared" si="1"/>
-        <v>0.95081967213114749</v>
+        <f t="shared" si="2"/>
+        <v>0.6</v>
       </c>
       <c r="K15" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.95081967213114749</v>
+        <v>0.6</v>
       </c>
       <c r="M15" s="4">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="N15" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P15" s="1">
-        <v>200</v>
+        <v>15</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q15" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="S15" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B16" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="C16" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E16" s="1">
         <v>300</v>
       </c>
       <c r="F16" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G16" s="1">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="H16" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I16" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="J16" s="1">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="K16" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
       <c r="M16" s="4">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="N16" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P16" s="1">
-        <v>300</v>
+        <v>15</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q16" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="S16" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B17" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="C17" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E17" s="1">
         <v>400</v>
       </c>
       <c r="F17" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G17" s="1">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="H17" s="1">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I17" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.45454545454545453</v>
+        <v>0</v>
       </c>
       <c r="J17" s="1">
-        <f t="shared" si="1"/>
-        <v>0.54545454545454541</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="K17" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.54545454545454541</v>
+        <v>1</v>
       </c>
       <c r="M17" s="4">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="N17" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P17" s="1">
-        <v>300</v>
+        <v>15</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q17" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S17" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B18" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="C18" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E18" s="1">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F18" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G18" s="1">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="H18" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.1038961038961039</v>
+        <v>0</v>
       </c>
       <c r="J18" s="1">
-        <f t="shared" si="1"/>
-        <v>0.89610389610389607</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="K18" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.89610389610389607</v>
+        <v>1</v>
       </c>
       <c r="M18" s="4">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="N18" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>30</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q18" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P18" s="1">
-        <v>300</v>
-      </c>
-      <c r="Q18" s="9">
-        <v>12264732</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="S18" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="C19" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E19" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F19" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G19" s="1">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="H19" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I19" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>8.1967213114754092E-2</v>
+        <v>0</v>
       </c>
       <c r="J19" s="1">
-        <f t="shared" si="1"/>
-        <v>0.91803278688524592</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="K19" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.91803278688524592</v>
+        <v>1</v>
       </c>
       <c r="M19" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="N19" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P19" s="1">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="Q19" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="S19" s="1">
-        <v>3</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="C20" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E20" s="1">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="F20" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G20" s="1">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="H20" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>5.4545454545454543E-2</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="J20" s="1">
-        <f t="shared" si="1"/>
-        <v>0.94545454545454544</v>
+        <f t="shared" si="2"/>
+        <v>0.77777777777777779</v>
       </c>
       <c r="K20" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.94545454545454544</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="M20" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="N20" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P20" s="1">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="Q20" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S20" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B21" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="C21" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E21" s="1">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="F21" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G21" s="1">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="H21" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>7.2727272727272724E-2</v>
+        <v>0</v>
       </c>
       <c r="J21" s="1">
-        <f t="shared" si="1"/>
-        <v>0.92727272727272725</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="K21" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.92727272727272725</v>
+        <v>1</v>
       </c>
       <c r="M21" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="N21" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P21" s="1">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="Q21" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S21" s="1">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B22" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="C22" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="E22" s="1">
+        <v>300</v>
       </c>
       <c r="F22" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G22" s="1">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H22" s="1">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I22" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>2.7777777777777776E-2</v>
+        <v>0.28260869565217389</v>
       </c>
       <c r="J22" s="1">
-        <f t="shared" si="1"/>
-        <v>0.97222222222222221</v>
+        <f t="shared" si="2"/>
+        <v>0.71739130434782616</v>
       </c>
       <c r="K22" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.97222222222222221</v>
+        <v>0.71739130434782616</v>
       </c>
       <c r="M22" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="N22" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P22" s="1">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="Q22" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="S22" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B23" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="C23" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
+      </c>
+      <c r="E23" s="1">
+        <v>400</v>
       </c>
       <c r="F23" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G23" s="1">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
@@ -25823,7 +25869,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <f>ABS(G$3-I23)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K23" s="5">
@@ -25831,47 +25877,47 @@
         <v>1</v>
       </c>
       <c r="M23" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="N23" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P23" s="1">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="Q23" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S23" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B24" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="C24" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E24" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F24" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="G24" s="1">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
@@ -25881,7 +25927,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <f t="shared" ref="J24:J32" si="2">ABS(G$3-I24)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K24" s="5">
@@ -25889,47 +25935,47 @@
         <v>1</v>
       </c>
       <c r="M24" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="N24" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P24" s="1">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="Q24" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="S24" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B25" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="C25" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E25" s="1">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="F25" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="G25" s="1">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -25939,7 +25985,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="J25:J32" si="3">ABS(G$3-I25)</f>
         <v>1</v>
       </c>
       <c r="K25" s="5">
@@ -25947,221 +25993,221 @@
         <v>1</v>
       </c>
       <c r="M25" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="N25" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P25" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="Q25" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="S25" s="1">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="C26" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E26" s="1">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="F26" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="G26" s="1">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I26" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="J26" s="1">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0.22222222222222221</v>
       </c>
       <c r="K26" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="M26" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="N26" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P26" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="Q26" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S26" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B27" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="C27" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E27" s="1">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="F27" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="G27" s="1">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H27" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="J27" s="1">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0.93333333333333335</v>
       </c>
       <c r="K27" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="M27" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="N27" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P27" s="1">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="Q27" s="9">
-        <v>12264732</v>
+        <v>12289475</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>31</v>
       </c>
       <c r="S27" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B28" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="C28" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E28" s="1">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F28" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G28" s="1">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="H28" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I28" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>6.6666666666666666E-2</v>
+        <v>7.9207920792079209E-2</v>
       </c>
       <c r="J28" s="1">
-        <f t="shared" si="2"/>
-        <v>0.93333333333333335</v>
+        <f t="shared" si="3"/>
+        <v>0.92079207920792083</v>
       </c>
       <c r="K28" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.93333333333333335</v>
+        <v>0.92079207920792083</v>
       </c>
       <c r="M28" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="N28" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P28" s="1">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="Q28" s="9">
-        <v>12264732</v>
+        <v>12289475</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="S28" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B29" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="C29" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E29" s="1">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="F29" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G29" s="1">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -26171,7 +26217,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K29" s="5">
@@ -26179,163 +26225,163 @@
         <v>1</v>
       </c>
       <c r="M29" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="N29" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P29" s="1">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="Q29" s="9">
-        <v>12264732</v>
+        <v>12289475</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="S29" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B30" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="C30" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E30" s="1">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="F30" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G30" s="1">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I30" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J30" s="1">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0.97</v>
       </c>
       <c r="K30" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M30" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="N30" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="P30" s="1">
+        <v>400</v>
       </c>
       <c r="Q30" s="9">
-        <v>12264732</v>
+        <v>12289475</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="S30" s="1">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="C31" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E31" s="1">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="F31" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G31" s="1">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I31" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.18965517241379309</v>
       </c>
       <c r="J31" s="1">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0.81034482758620685</v>
       </c>
       <c r="K31" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.81034482758620685</v>
       </c>
       <c r="M31" s="4">
-        <v>46223</v>
-      </c>
-      <c r="N31" s="12">
+        <v>46234</v>
+      </c>
+      <c r="N31" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O31" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P31" s="1">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="Q31" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S31" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="C32" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="E32" s="1">
+        <v>500</v>
       </c>
       <c r="F32" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G32" s="1">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -26345,7 +26391,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K32" s="5">
@@ -26353,511 +26399,511 @@
         <v>1</v>
       </c>
       <c r="M32" s="4">
-        <v>46223</v>
-      </c>
-      <c r="N32" s="12">
+        <v>46234</v>
+      </c>
+      <c r="N32" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O32" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P32" s="1">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="Q32" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="S32" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B33" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="C33" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
+      </c>
+      <c r="E33" s="1">
+        <v>600</v>
       </c>
       <c r="F33" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G33" s="1">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="H33" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I33" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>5.3191489361702128E-2</v>
       </c>
       <c r="J33" s="1">
-        <f>ABS(G$3-I33)</f>
-        <v>1</v>
+        <f t="shared" ref="J33:J37" si="4">ABS(G$3-I33)</f>
+        <v>0.94680851063829785</v>
       </c>
       <c r="K33" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.94680851063829785</v>
       </c>
       <c r="M33" s="4">
-        <v>46223</v>
-      </c>
-      <c r="N33" s="12">
+        <v>46234</v>
+      </c>
+      <c r="N33" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O33" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O33" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P33" s="1">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="Q33" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="S33" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
-        <v>46223</v>
+        <v>46234</v>
       </c>
       <c r="C34" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E34" s="1">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="F34" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G34" s="1">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I34" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>4.2553191489361701E-2</v>
       </c>
       <c r="J34" s="1">
-        <f t="shared" ref="J34:J44" si="3">ABS(G$3-I34)</f>
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>0.95744680851063835</v>
       </c>
       <c r="K34" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.95744680851063835</v>
       </c>
       <c r="M34" s="4">
-        <v>46223</v>
-      </c>
-      <c r="N34" s="12">
+        <v>46234</v>
+      </c>
+      <c r="N34" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O34" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P34" s="1">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="Q34" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="S34" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B35" s="4">
-        <v>46223</v>
+        <v>46234</v>
       </c>
       <c r="C35" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E35" s="1">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="F35" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G35" s="1">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="H35" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>1.4492753623188406E-2</v>
+        <v>0</v>
       </c>
       <c r="J35" s="1">
-        <f t="shared" si="3"/>
-        <v>0.98550724637681164</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="K35" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.98550724637681164</v>
+        <v>1</v>
       </c>
       <c r="M35" s="4">
-        <v>46223</v>
-      </c>
-      <c r="N35" s="12">
+        <v>46238</v>
+      </c>
+      <c r="N35" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O35" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P35" s="1">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="Q35" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="S35" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B36" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="C36" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E36" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F36" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G36" s="1">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="H36" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I36" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>6.0606060606060608E-2</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="J36" s="1">
-        <f t="shared" si="3"/>
-        <v>0.93939393939393945</v>
+        <f t="shared" si="4"/>
+        <v>0.15384615384615385</v>
       </c>
       <c r="K36" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.93939393939393945</v>
+        <v>0.15384615384615385</v>
       </c>
       <c r="M36" s="4">
-        <v>46223</v>
-      </c>
-      <c r="N36" s="12">
+        <v>46238</v>
+      </c>
+      <c r="N36" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O36" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O36" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P36" s="1">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="Q36" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="S36" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B37" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="C37" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E37" s="1">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F37" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G37" s="1">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="H37" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I37" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="J37" s="1">
-        <f t="shared" si="3"/>
-        <v>0.52</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="K37" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.52</v>
+        <v>1</v>
       </c>
       <c r="M37" s="4">
-        <v>46223</v>
-      </c>
-      <c r="N37" s="12">
+        <v>46238</v>
+      </c>
+      <c r="N37" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O37" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O37" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P37" s="1">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="Q37" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="S37" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B38" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="C38" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E38" s="1">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="F38" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G38" s="1">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H38" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I38" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.11428571428571428</v>
+        <v>0</v>
       </c>
       <c r="J38" s="1">
-        <f t="shared" si="3"/>
-        <v>0.88571428571428568</v>
+        <f t="shared" ref="J38:J45" si="5">ABS(G$3-I38)</f>
+        <v>1</v>
       </c>
       <c r="K38" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.88571428571428568</v>
+        <v>1</v>
       </c>
       <c r="M38" s="4">
-        <v>46223</v>
-      </c>
-      <c r="N38" s="12">
+        <v>46238</v>
+      </c>
+      <c r="N38" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O38" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O38" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P38" s="1">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="Q38" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="S38" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B39" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="C39" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E39" s="1">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="F39" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G39" s="1">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H39" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I39" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.25714285714285712</v>
+        <v>0</v>
       </c>
       <c r="J39" s="1">
-        <f t="shared" si="3"/>
-        <v>0.74285714285714288</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="K39" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.74285714285714288</v>
+        <v>1</v>
       </c>
       <c r="M39" s="4">
-        <v>46223</v>
-      </c>
-      <c r="N39" s="12">
+        <v>46238</v>
+      </c>
+      <c r="N39" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O39" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O39" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P39" s="1">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="Q39" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="S39" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B40" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="C40" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E40" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="F40" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G40" s="1">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H40" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I40" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J40" s="1">
-        <f t="shared" si="3"/>
-        <v>0.6</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="K40" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M40" s="4">
-        <v>46223</v>
-      </c>
-      <c r="N40" s="12">
+        <v>46238</v>
+      </c>
+      <c r="N40" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O40" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O40" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P40" s="1">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="Q40" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="S40" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="C41" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E41" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="F41" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G41" s="1">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
@@ -26867,7 +26913,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K41" s="5">
@@ -26875,47 +26921,47 @@
         <v>1</v>
       </c>
       <c r="M41" s="4">
-        <v>46223</v>
-      </c>
-      <c r="N41" s="12">
+        <v>46238</v>
+      </c>
+      <c r="N41" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O41" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O41" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P41" s="1">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="Q41" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="S41" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B42" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="C42" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>15</v>
+      <c r="E42" s="1">
+        <v>700</v>
       </c>
       <c r="F42" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G42" s="1">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -26925,7 +26971,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K42" s="5">
@@ -26933,47 +26979,47 @@
         <v>1</v>
       </c>
       <c r="M42" s="4">
-        <v>46223</v>
-      </c>
-      <c r="N42" s="12">
+        <v>46232</v>
+      </c>
+      <c r="N42" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P42" s="1">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="Q42" s="9">
-        <v>12264714</v>
+        <v>10532587</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="S42" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B43" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="C43" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>17</v>
+      <c r="E43" s="1">
+        <v>800</v>
       </c>
       <c r="F43" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G43" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -26983,7 +27029,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K43" s="5">
@@ -26991,255 +27037,255 @@
         <v>1</v>
       </c>
       <c r="M43" s="4">
-        <v>46223</v>
+        <v>46232</v>
       </c>
       <c r="N43" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P43" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q43" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S43" s="1">
         <v>18</v>
-      </c>
-      <c r="P43" s="1">
-        <v>800</v>
-      </c>
-      <c r="Q43" s="9">
-        <v>12264714</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S43" s="1">
-        <v>14</v>
       </c>
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
-        <v>46227</v>
+        <v>46238</v>
       </c>
       <c r="C44" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="E44" s="1">
         <v>100</v>
       </c>
       <c r="F44" s="9">
-        <v>12260416</v>
+        <v>12289497</v>
       </c>
       <c r="G44" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H44" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I44" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J44" s="1">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.5</v>
       </c>
       <c r="K44" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M44" s="4">
-        <v>46227</v>
-      </c>
-      <c r="N44" s="12">
+        <v>46232</v>
+      </c>
+      <c r="N44" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P44" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q44" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="S44" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B45" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C45" s="12">
+        <v>46238</v>
+      </c>
+      <c r="C45" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="E45" s="1">
         <v>200</v>
       </c>
       <c r="F45" s="9">
-        <v>12260416</v>
+        <v>12289497</v>
       </c>
       <c r="G45" s="1">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H45" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I45" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.04</v>
-      </c>
-      <c r="J45" s="12">
-        <f t="shared" ref="J45:J52" si="4">ABS(G$3-I45)</f>
-        <v>0.96</v>
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="J45" s="1">
+        <f t="shared" si="5"/>
+        <v>0.7857142857142857</v>
       </c>
       <c r="K45" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.96</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="M45" s="4">
-        <v>46227</v>
-      </c>
-      <c r="N45" s="12">
+        <v>46232</v>
+      </c>
+      <c r="N45" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P45" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q45" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="S45" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B46" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C46" s="12">
+        <v>46238</v>
+      </c>
+      <c r="C46" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="E46" s="1">
         <v>300</v>
       </c>
       <c r="F46" s="9">
-        <v>12260416</v>
+        <v>12289497</v>
       </c>
       <c r="G46" s="1">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="H46" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I46" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.25</v>
-      </c>
-      <c r="J46" s="12">
-        <f t="shared" si="4"/>
-        <v>0.75</v>
+        <v>0</v>
+      </c>
+      <c r="J46" s="1">
+        <f t="shared" ref="J46:J51" si="6">ABS(G$3-I46)</f>
+        <v>1</v>
       </c>
       <c r="K46" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M46" s="4">
-        <v>46227</v>
-      </c>
-      <c r="N46" s="12">
+        <v>46232</v>
+      </c>
+      <c r="N46" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P46" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q46" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="S46" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C47" s="12">
+        <v>46238</v>
+      </c>
+      <c r="C47" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="E47" s="1">
         <v>400</v>
       </c>
       <c r="F47" s="9">
-        <v>12260416</v>
+        <v>12289497</v>
       </c>
       <c r="G47" s="1">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="H47" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.5</v>
-      </c>
-      <c r="J47" s="12">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="K47" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M47" s="4">
-        <v>46227</v>
-      </c>
-      <c r="N47" s="12">
+        <v>46232</v>
+      </c>
+      <c r="N47" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P47" s="1">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Q47" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="S47" s="1">
         <v>6</v>
@@ -27247,197 +27293,197 @@
     </row>
     <row r="48" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C48" s="12">
+        <v>46238</v>
+      </c>
+      <c r="C48" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E48" s="1">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F48" s="9">
-        <v>12260416</v>
+        <v>12289497</v>
       </c>
       <c r="G48" s="1">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="H48" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I48" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.2</v>
-      </c>
-      <c r="J48" s="12">
-        <f t="shared" si="4"/>
-        <v>0.8</v>
+        <v>0.11904761904761904</v>
+      </c>
+      <c r="J48" s="1">
+        <f t="shared" si="6"/>
+        <v>0.88095238095238093</v>
       </c>
       <c r="K48" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.8</v>
+        <v>0.88095238095238093</v>
       </c>
       <c r="M48" s="4">
-        <v>46227</v>
-      </c>
-      <c r="N48" s="12">
+        <v>46232</v>
+      </c>
+      <c r="N48" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P48" s="1">
-        <v>400</v>
+        <v>15</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q48" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="S48" s="1">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B49" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C49" s="12">
+        <v>46238</v>
+      </c>
+      <c r="C49" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E49" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F49" s="9">
-        <v>12260416</v>
+        <v>12289497</v>
       </c>
       <c r="G49" s="1">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="H49" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.69230769230769229</v>
-      </c>
-      <c r="J49" s="12">
-        <f t="shared" si="4"/>
-        <v>0.30769230769230771</v>
+        <v>0</v>
+      </c>
+      <c r="J49" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="K49" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.30769230769230771</v>
+        <v>1</v>
       </c>
       <c r="M49" s="4">
-        <v>46227</v>
-      </c>
-      <c r="N49" s="12">
+        <v>46232</v>
+      </c>
+      <c r="N49" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P49" s="1">
-        <v>400</v>
+        <v>15</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q49" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S49" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B50" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C50" s="12">
+        <v>46238</v>
+      </c>
+      <c r="C50" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E50" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F50" s="9">
-        <v>12260416</v>
+        <v>12289497</v>
       </c>
       <c r="G50" s="1">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H50" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I50" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>5.2631578947368418E-2</v>
-      </c>
-      <c r="J50" s="12">
-        <f t="shared" si="4"/>
-        <v>0.94736842105263164</v>
+        <v>0</v>
+      </c>
+      <c r="J50" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="K50" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.94736842105263164</v>
+        <v>1</v>
       </c>
       <c r="M50" s="4">
-        <v>46227</v>
-      </c>
-      <c r="N50" s="12">
+        <v>46232</v>
+      </c>
+      <c r="N50" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P50" s="1">
-        <v>400</v>
+        <v>15</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q50" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="S50" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B51" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C51" s="12">
+        <v>46238</v>
+      </c>
+      <c r="C51" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E51" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F51" s="9">
-        <v>12260416</v>
+        <v>12289497</v>
       </c>
       <c r="G51" s="1">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
@@ -27446,8 +27492,8 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J51" s="12">
-        <f t="shared" si="4"/>
+      <c r="J51" s="1">
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K51" s="5">
@@ -27455,337 +27501,337 @@
         <v>1</v>
       </c>
       <c r="M51" s="4">
-        <v>46227</v>
-      </c>
-      <c r="N51" s="12">
+        <v>46232</v>
+      </c>
+      <c r="N51" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P51" s="1">
-        <v>400</v>
+        <v>15</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q51" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="S51" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B52" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C52" s="12">
+        <v>46232</v>
+      </c>
+      <c r="C52" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E52" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="E52" s="1">
+        <v>100</v>
+      </c>
       <c r="F52" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="G52" s="1">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="H52" s="1">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="I52" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.1875</v>
-      </c>
-      <c r="J52" s="12">
-        <f t="shared" si="4"/>
-        <v>0.8125</v>
+        <v>0.25833333333333336</v>
+      </c>
+      <c r="J52" s="1">
+        <f t="shared" ref="J52:J60" si="7">ABS(G$3-I52)</f>
+        <v>0.7416666666666667</v>
       </c>
       <c r="K52" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.8125</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="M52" s="4">
-        <v>46227</v>
-      </c>
-      <c r="N52" s="12">
+        <v>46239</v>
+      </c>
+      <c r="N52" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P52" s="1">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="Q52" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="S52" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B53" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C53" s="12">
+        <v>46232</v>
+      </c>
+      <c r="C53" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="E53" s="1">
+        <v>150</v>
       </c>
       <c r="F53" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="G53" s="1">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="H53" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I53" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
-      </c>
-      <c r="J53" s="12">
-        <f>ABS(G$3-I53)</f>
-        <v>1</v>
+        <v>8.5714285714285715E-2</v>
+      </c>
+      <c r="J53" s="1">
+        <f t="shared" si="7"/>
+        <v>0.91428571428571426</v>
       </c>
       <c r="K53" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.91428571428571426</v>
       </c>
       <c r="M53" s="4">
-        <v>46227</v>
-      </c>
-      <c r="N53" s="12">
+        <v>46239</v>
+      </c>
+      <c r="N53" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P53" s="1">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="Q53" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="S53" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B54" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C54" s="12">
+        <v>46232</v>
+      </c>
+      <c r="C54" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E54" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F54" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G54" s="1">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="H54" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I54" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
-      </c>
-      <c r="J54" s="12">
-        <f t="shared" ref="J54:J61" si="5">ABS(G$3-I54)</f>
-        <v>1</v>
+        <v>0.15238095238095239</v>
+      </c>
+      <c r="J54" s="1">
+        <f t="shared" si="7"/>
+        <v>0.84761904761904761</v>
       </c>
       <c r="K54" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.84761904761904761</v>
       </c>
       <c r="M54" s="4">
-        <v>46227</v>
-      </c>
-      <c r="N54" s="12">
+        <v>46239</v>
+      </c>
+      <c r="N54" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P54" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q54" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S54" s="1">
         <v>18</v>
-      </c>
-      <c r="P54" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q54" s="9">
-        <v>12260416</v>
-      </c>
-      <c r="R54" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="S54" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="55" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B55" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C55" s="12">
+        <v>46232</v>
+      </c>
+      <c r="C55" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E55" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F55" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G55" s="1">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="H55" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I55" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
-      </c>
-      <c r="J55" s="12">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>5.9405940594059403E-2</v>
+      </c>
+      <c r="J55" s="1">
+        <f t="shared" si="7"/>
+        <v>0.94059405940594054</v>
       </c>
       <c r="K55" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.94059405940594054</v>
       </c>
       <c r="M55" s="4">
-        <v>46227</v>
-      </c>
-      <c r="N55" s="12">
+        <v>46237</v>
+      </c>
+      <c r="N55" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P55" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="P55" s="1">
+        <v>300</v>
+      </c>
       <c r="Q55" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="S55" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C56" s="12">
+        <v>46232</v>
+      </c>
+      <c r="C56" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E56" s="1">
-        <v>300</v>
+        <v>15</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F56" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G56" s="1">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="H56" s="1">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I56" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
-      </c>
-      <c r="J56" s="12">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.7068965517241379</v>
+      </c>
+      <c r="J56" s="1">
+        <f t="shared" si="7"/>
+        <v>0.2931034482758621</v>
       </c>
       <c r="K56" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.2931034482758621</v>
       </c>
       <c r="M56" s="4">
-        <v>46227</v>
-      </c>
-      <c r="N56" s="12">
+        <v>46239</v>
+      </c>
+      <c r="N56" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P56" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="P56" s="1">
+        <v>300</v>
+      </c>
       <c r="Q56" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="S56" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B57" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C57" s="12">
+        <v>46237</v>
+      </c>
+      <c r="C57" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E57" s="1">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F57" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G57" s="1">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
@@ -27794,8 +27840,8 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J57" s="12">
-        <f t="shared" si="5"/>
+      <c r="J57" s="1">
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K57" s="5">
@@ -27803,417 +27849,717 @@
         <v>1</v>
       </c>
       <c r="M57" s="4">
-        <v>46227</v>
-      </c>
-      <c r="N57" s="12">
+        <v>46239</v>
+      </c>
+      <c r="N57" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P57" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="P57" s="1">
+        <v>300</v>
+      </c>
       <c r="Q57" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S57" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B58" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C58" s="12">
+        <v>46237</v>
+      </c>
+      <c r="C58" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E58" s="1">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="F58" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G58" s="1">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="H58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.15789473684210525</v>
-      </c>
-      <c r="J58" s="12">
-        <f t="shared" si="5"/>
-        <v>0.84210526315789469</v>
+        <v>0</v>
+      </c>
+      <c r="J58" s="1">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="K58" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.84210526315789469</v>
+        <v>1</v>
       </c>
       <c r="M58" s="4">
-        <v>46220</v>
-      </c>
-      <c r="N58" s="12">
+        <v>46237</v>
+      </c>
+      <c r="N58" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q58" s="9">
-        <v>12264714</v>
+        <v>10532587</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="S58" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B59" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C59" s="12">
+        <v>46237</v>
+      </c>
+      <c r="C59" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E59" s="1">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="F59" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G59" s="1">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="H59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="J59" s="12">
-        <f t="shared" si="5"/>
-        <v>0.94444444444444442</v>
+        <v>0</v>
+      </c>
+      <c r="J59" s="1">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="K59" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.94444444444444442</v>
+        <v>1</v>
       </c>
       <c r="M59" s="4">
-        <v>46227</v>
-      </c>
-      <c r="N59" s="12">
+        <v>46237</v>
+      </c>
+      <c r="N59" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P59" s="1">
-        <v>600</v>
+        <v>15</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q59" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="S59" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B60" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C60" s="12">
+        <v>46237</v>
+      </c>
+      <c r="C60" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E60" s="1">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="F60" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G60" s="1">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="H60" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I60" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.22222222222222221</v>
-      </c>
-      <c r="J60" s="12">
-        <f t="shared" si="5"/>
-        <v>0.77777777777777779</v>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="J60" s="1">
+        <f t="shared" si="7"/>
+        <v>0.96551724137931039</v>
       </c>
       <c r="K60" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.77777777777777779</v>
+        <v>0.96551724137931039</v>
       </c>
       <c r="M60" s="4">
-        <v>46227</v>
-      </c>
-      <c r="N60" s="12">
+        <v>46237</v>
+      </c>
+      <c r="N60" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P60" s="1">
-        <v>700</v>
+        <v>15</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q60" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="S60" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C61" s="12">
+        <v>46237</v>
+      </c>
+      <c r="C61" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E61" s="1">
-        <v>900</v>
+        <v>15</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F61" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G61" s="1">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="H61" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I61" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
-      </c>
-      <c r="J61" s="12">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.16</v>
+      </c>
+      <c r="J61" s="1">
+        <f>ABS(G$3-I61)</f>
+        <v>0.84</v>
       </c>
       <c r="K61" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="M61" s="4">
-        <v>46227</v>
-      </c>
-      <c r="N61" s="12">
+        <v>46237</v>
+      </c>
+      <c r="N61" s="1">
         <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P61" s="1">
-        <v>800</v>
+        <v>15</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q61" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="S61" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
-        <v>46227</v>
-      </c>
-      <c r="C62" s="12">
+        <v>46239</v>
+      </c>
+      <c r="C62" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="E62" s="1">
+        <v>100</v>
+      </c>
       <c r="F62" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G62" s="1">
-        <v>40</v>
+        <v>219</v>
       </c>
       <c r="H62" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I62" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
-      </c>
-      <c r="J62" s="12">
-        <f t="shared" ref="J62" si="6">ABS(G$3-I62)</f>
-        <v>1</v>
+        <v>6.3926940639269403E-2</v>
+      </c>
+      <c r="J62" s="1">
+        <f t="shared" ref="J62:J66" si="8">ABS(G$3-I62)</f>
+        <v>0.9360730593607306</v>
       </c>
       <c r="K62" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.9360730593607306</v>
+      </c>
+      <c r="M62" s="4">
+        <v>46237</v>
+      </c>
+      <c r="N62" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q62" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R62" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S62" s="1">
         <v>1</v>
       </c>
-      <c r="M62" s="4"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B63" s="4"/>
-      <c r="I63" s="3"/>
-      <c r="J63" s="1"/>
-      <c r="K63" s="5"/>
-      <c r="M63" s="4"/>
+      <c r="B63" s="4">
+        <v>46239</v>
+      </c>
+      <c r="C63" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" s="1">
+        <v>150</v>
+      </c>
+      <c r="F63" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G63" s="1">
+        <v>219</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="1">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K63" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M63" s="4">
+        <v>46237</v>
+      </c>
+      <c r="N63" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P63" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q63" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R63" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S63" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B64" s="4"/>
-      <c r="I64" s="3"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="5"/>
-      <c r="M64" s="4"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B65" s="4"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="1"/>
-      <c r="K65" s="5"/>
-      <c r="M65" s="4"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B66" s="4"/>
-      <c r="I66" s="3"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="5"/>
-      <c r="M66" s="4"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B67" s="4"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="5"/>
-      <c r="M67" s="4"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B64" s="4">
+        <v>46239</v>
+      </c>
+      <c r="C64" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" s="1">
+        <v>200</v>
+      </c>
+      <c r="F64" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G64" s="1">
+        <v>216</v>
+      </c>
+      <c r="H64" s="1">
+        <v>18</v>
+      </c>
+      <c r="I64" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="J64" s="1">
+        <f t="shared" si="8"/>
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="K64" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="M64" s="4">
+        <v>46239</v>
+      </c>
+      <c r="N64" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q64" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R64" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S64" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B65" s="4">
+        <v>46239</v>
+      </c>
+      <c r="C65" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" s="1">
+        <v>300</v>
+      </c>
+      <c r="F65" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G65" s="1">
+        <v>210</v>
+      </c>
+      <c r="H65" s="1">
+        <v>8</v>
+      </c>
+      <c r="I65" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>3.8095238095238099E-2</v>
+      </c>
+      <c r="J65" s="1">
+        <f t="shared" si="8"/>
+        <v>0.96190476190476193</v>
+      </c>
+      <c r="K65" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.96190476190476193</v>
+      </c>
+      <c r="M65" s="4">
+        <v>46239</v>
+      </c>
+      <c r="N65" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q65" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R65" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S65" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B66" s="4">
+        <v>46239</v>
+      </c>
+      <c r="C66" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F66" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G66" s="1">
+        <v>187</v>
+      </c>
+      <c r="H66" s="1">
+        <v>24</v>
+      </c>
+      <c r="I66" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.12834224598930483</v>
+      </c>
+      <c r="J66" s="1">
+        <f t="shared" si="8"/>
+        <v>0.87165775401069512</v>
+      </c>
+      <c r="K66" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.87165775401069512</v>
+      </c>
+      <c r="M66" s="4">
+        <v>46239</v>
+      </c>
+      <c r="N66" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q66" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R66" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S66" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="12">
+        <v>46254</v>
+      </c>
+      <c r="C67" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>34</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F67" s="14">
+        <v>10532587</v>
+      </c>
+      <c r="G67" s="13">
+        <v>200</v>
+      </c>
+      <c r="H67" s="13">
+        <v>2</v>
+      </c>
+      <c r="I67" s="15">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="J67" s="13">
+        <f>ABS(G$3-I67)</f>
+        <v>0.99</v>
+      </c>
+      <c r="K67" s="16">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.99</v>
+      </c>
+      <c r="M67" s="12">
+        <v>46254</v>
+      </c>
+      <c r="N67" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>34</v>
+      </c>
+      <c r="O67" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="P67" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q67" s="14">
+        <v>10532587</v>
+      </c>
+      <c r="R67" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="S67" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B68" s="4"/>
+      <c r="G68" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="I68" s="3"/>
       <c r="J68" s="1"/>
       <c r="K68" s="5"/>
-      <c r="M68" s="4"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M68" s="4">
+        <v>46254</v>
+      </c>
+      <c r="N68" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>34</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P68" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q68" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R68" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S68" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B69" s="4"/>
       <c r="I69" s="3"/>
       <c r="J69" s="1"/>
       <c r="K69" s="5"/>
       <c r="M69" s="4"/>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B70" s="4"/>
       <c r="I70" s="3"/>
       <c r="J70" s="1"/>
       <c r="K70" s="5"/>
       <c r="M70" s="4"/>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B71" s="4"/>
       <c r="I71" s="3"/>
       <c r="J71" s="1"/>
       <c r="K71" s="5"/>
       <c r="M71" s="4"/>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B72" s="4"/>
       <c r="I72" s="3"/>
       <c r="J72" s="1"/>
       <c r="K72" s="5"/>
       <c r="M72" s="4"/>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B73" s="4"/>
       <c r="I73" s="3"/>
       <c r="J73" s="1"/>
       <c r="K73" s="5"/>
       <c r="M73" s="4"/>
     </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B74" s="4"/>
       <c r="I74" s="3"/>
       <c r="J74" s="1"/>
       <c r="K74" s="5"/>
       <c r="M74" s="4"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B75" s="4"/>
       <c r="I75" s="3"/>
       <c r="J75" s="1"/>
       <c r="K75" s="5"/>
       <c r="M75" s="4"/>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B76" s="4"/>
       <c r="I76" s="3"/>
       <c r="J76" s="1"/>
       <c r="K76" s="5"/>
       <c r="M76" s="4"/>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B77" s="4"/>
       <c r="I77" s="3"/>
       <c r="J77" s="1"/>
       <c r="K77" s="5"/>
       <c r="M77" s="4"/>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B78" s="4"/>
       <c r="I78" s="3"/>
       <c r="J78" s="1"/>
       <c r="K78" s="5"/>
       <c r="M78" s="4"/>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B79" s="4"/>
       <c r="I79" s="3"/>
       <c r="J79" s="1"/>
       <c r="K79" s="5"/>
       <c r="M79" s="4"/>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B80" s="4"/>
       <c r="I80" s="3"/>
       <c r="J80" s="1"/>
@@ -29192,6 +29538,8 @@
       <c r="J219" s="1"/>
       <c r="K219" s="5"/>
       <c r="M219" s="4"/>
+      <c r="U219" s="1"/>
+      <c r="V219" s="1"/>
     </row>
     <row r="220" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B220" s="4"/>
@@ -29199,6 +29547,8 @@
       <c r="J220" s="1"/>
       <c r="K220" s="5"/>
       <c r="M220" s="4"/>
+      <c r="U220" s="1"/>
+      <c r="V220" s="1"/>
     </row>
     <row r="221" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B221" s="4"/>
@@ -29206,8 +29556,6 @@
       <c r="J221" s="1"/>
       <c r="K221" s="5"/>
       <c r="M221" s="4"/>
-      <c r="U221" s="1"/>
-      <c r="V221" s="1"/>
     </row>
     <row r="222" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B222" s="4"/>
@@ -29215,8 +29563,6 @@
       <c r="J222" s="1"/>
       <c r="K222" s="5"/>
       <c r="M222" s="4"/>
-      <c r="U222" s="1"/>
-      <c r="V222" s="1"/>
     </row>
     <row r="223" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B223" s="4"/>
@@ -29314,14 +29660,14 @@
       <c r="I236" s="3"/>
       <c r="J236" s="1"/>
       <c r="K236" s="5"/>
-      <c r="M236" s="4"/>
+      <c r="M236" s="8"/>
     </row>
     <row r="237" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B237" s="4"/>
       <c r="I237" s="3"/>
       <c r="J237" s="1"/>
       <c r="K237" s="5"/>
-      <c r="M237" s="4"/>
+      <c r="M237" s="8"/>
     </row>
     <row r="238" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B238" s="4"/>
@@ -29335,14 +29681,14 @@
       <c r="I239" s="3"/>
       <c r="J239" s="1"/>
       <c r="K239" s="5"/>
-      <c r="M239" s="8"/>
+      <c r="M239" s="4"/>
     </row>
     <row r="240" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B240" s="4"/>
       <c r="I240" s="3"/>
       <c r="J240" s="1"/>
       <c r="K240" s="5"/>
-      <c r="M240" s="8"/>
+      <c r="M240" s="4"/>
     </row>
     <row r="241" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B241" s="4"/>
@@ -29621,14 +29967,12 @@
       <c r="B280" s="4"/>
       <c r="I280" s="3"/>
       <c r="J280" s="1"/>
-      <c r="K280" s="5"/>
       <c r="M280" s="4"/>
     </row>
     <row r="281" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B281" s="4"/>
       <c r="I281" s="3"/>
       <c r="J281" s="1"/>
-      <c r="K281" s="5"/>
       <c r="M281" s="4"/>
     </row>
     <row r="282" spans="2:13" x14ac:dyDescent="0.3">
@@ -29647,13 +29991,11 @@
       <c r="B284" s="4"/>
       <c r="I284" s="3"/>
       <c r="J284" s="1"/>
-      <c r="M284" s="4"/>
     </row>
     <row r="285" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B285" s="4"/>
       <c r="I285" s="3"/>
       <c r="J285" s="1"/>
-      <c r="M285" s="4"/>
     </row>
     <row r="286" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B286" s="4"/>
@@ -29736,6 +30078,9 @@
       <c r="J301" s="1"/>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>0</v>
+      </c>
       <c r="B302" s="4"/>
       <c r="I302" s="3"/>
       <c r="J302" s="1"/>
@@ -29746,9 +30091,6 @@
       <c r="J303" s="1"/>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A304" t="s">
-        <v>0</v>
-      </c>
       <c r="B304" s="4"/>
       <c r="I304" s="3"/>
       <c r="J304" s="1"/>
@@ -29939,6 +30281,9 @@
       <c r="J341" s="1"/>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>0</v>
+      </c>
       <c r="B342" s="4"/>
       <c r="I342" s="3"/>
       <c r="J342" s="1"/>
@@ -29949,9 +30294,6 @@
       <c r="J343" s="1"/>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A344" t="s">
-        <v>0</v>
-      </c>
       <c r="B344" s="4"/>
       <c r="I344" s="3"/>
       <c r="J344" s="1"/>
@@ -30365,11 +30707,17 @@
       <c r="B426" s="4"/>
       <c r="I426" s="3"/>
       <c r="J426" s="1"/>
+      <c r="M426" s="7"/>
+      <c r="N426" s="7"/>
+      <c r="O426" s="7"/>
     </row>
     <row r="427" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B427" s="4"/>
       <c r="I427" s="3"/>
       <c r="J427" s="1"/>
+      <c r="M427" s="7"/>
+      <c r="N427" s="7"/>
+      <c r="O427" s="7"/>
     </row>
     <row r="428" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B428" s="4"/>
@@ -30512,7 +30860,7 @@
       <c r="I445" s="3"/>
       <c r="J445" s="1"/>
       <c r="M445" s="7"/>
-      <c r="N445" s="7"/>
+      <c r="N445" s="8"/>
       <c r="O445" s="7"/>
     </row>
     <row r="446" spans="2:15" x14ac:dyDescent="0.3">
@@ -30528,7 +30876,7 @@
       <c r="I447" s="3"/>
       <c r="J447" s="1"/>
       <c r="M447" s="7"/>
-      <c r="N447" s="8"/>
+      <c r="N447" s="7"/>
       <c r="O447" s="7"/>
     </row>
     <row r="448" spans="2:15" x14ac:dyDescent="0.3">
@@ -30743,17 +31091,11 @@
       <c r="B474" s="4"/>
       <c r="I474" s="3"/>
       <c r="J474" s="1"/>
-      <c r="M474" s="7"/>
-      <c r="N474" s="7"/>
-      <c r="O474" s="7"/>
     </row>
     <row r="475" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B475" s="4"/>
       <c r="I475" s="3"/>
       <c r="J475" s="1"/>
-      <c r="M475" s="7"/>
-      <c r="N475" s="7"/>
-      <c r="O475" s="7"/>
     </row>
     <row r="476" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B476" s="4"/>
@@ -31781,6 +32123,9 @@
       <c r="J680" s="1"/>
     </row>
     <row r="681" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A681" t="s">
+        <v>0</v>
+      </c>
       <c r="B681" s="4"/>
       <c r="I681" s="3"/>
       <c r="J681" s="1"/>
@@ -31791,9 +32136,6 @@
       <c r="J682" s="1"/>
     </row>
     <row r="683" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A683" t="s">
-        <v>0</v>
-      </c>
       <c r="B683" s="4"/>
       <c r="I683" s="3"/>
       <c r="J683" s="1"/>
@@ -31814,6 +32156,9 @@
       <c r="J686" s="1"/>
     </row>
     <row r="687" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A687" t="s">
+        <v>0</v>
+      </c>
       <c r="B687" s="4"/>
       <c r="I687" s="3"/>
       <c r="J687" s="1"/>
@@ -31824,9 +32169,6 @@
       <c r="J688" s="1"/>
     </row>
     <row r="689" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A689" t="s">
-        <v>0</v>
-      </c>
       <c r="B689" s="4"/>
       <c r="I689" s="3"/>
       <c r="J689" s="1"/>
@@ -31847,6 +32189,9 @@
       <c r="J692" s="1"/>
     </row>
     <row r="693" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A693" t="s">
+        <v>0</v>
+      </c>
       <c r="B693" s="4"/>
       <c r="I693" s="3"/>
       <c r="J693" s="1"/>
@@ -31857,9 +32202,6 @@
       <c r="J694" s="1"/>
     </row>
     <row r="695" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A695" t="s">
-        <v>0</v>
-      </c>
       <c r="B695" s="4"/>
       <c r="I695" s="3"/>
       <c r="J695" s="1"/>
@@ -31880,6 +32222,9 @@
       <c r="J698" s="1"/>
     </row>
     <row r="699" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A699" t="s">
+        <v>0</v>
+      </c>
       <c r="B699" s="4"/>
       <c r="I699" s="3"/>
       <c r="J699" s="1"/>
@@ -31890,9 +32235,6 @@
       <c r="J700" s="1"/>
     </row>
     <row r="701" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A701" t="s">
-        <v>0</v>
-      </c>
       <c r="B701" s="4"/>
       <c r="I701" s="3"/>
       <c r="J701" s="1"/>
@@ -31913,6 +32255,9 @@
       <c r="J704" s="1"/>
     </row>
     <row r="705" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A705" t="s">
+        <v>0</v>
+      </c>
       <c r="B705" s="4"/>
       <c r="I705" s="3"/>
       <c r="J705" s="1"/>
@@ -31923,9 +32268,6 @@
       <c r="J706" s="1"/>
     </row>
     <row r="707" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A707" t="s">
-        <v>0</v>
-      </c>
       <c r="B707" s="4"/>
       <c r="I707" s="3"/>
       <c r="J707" s="1"/>
@@ -31946,6 +32288,9 @@
       <c r="J710" s="1"/>
     </row>
     <row r="711" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A711" t="s">
+        <v>0</v>
+      </c>
       <c r="B711" s="4"/>
       <c r="I711" s="3"/>
       <c r="J711" s="1"/>
@@ -31956,9 +32301,6 @@
       <c r="J712" s="1"/>
     </row>
     <row r="713" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A713" t="s">
-        <v>0</v>
-      </c>
       <c r="B713" s="4"/>
       <c r="I713" s="3"/>
       <c r="J713" s="1"/>
@@ -31998,170 +32340,173 @@
       <c r="I720" s="3"/>
       <c r="J720" s="1"/>
     </row>
-    <row r="721" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B721" s="4"/>
       <c r="I721" s="3"/>
       <c r="J721" s="1"/>
     </row>
-    <row r="722" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B722" s="4"/>
       <c r="I722" s="3"/>
       <c r="J722" s="1"/>
     </row>
-    <row r="723" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B723" s="4"/>
       <c r="I723" s="3"/>
       <c r="J723" s="1"/>
     </row>
-    <row r="724" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B724" s="4"/>
       <c r="I724" s="3"/>
       <c r="J724" s="1"/>
     </row>
-    <row r="725" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B725" s="4"/>
       <c r="I725" s="3"/>
       <c r="J725" s="1"/>
     </row>
-    <row r="726" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B726" s="4"/>
       <c r="I726" s="3"/>
       <c r="J726" s="1"/>
     </row>
-    <row r="727" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B727" s="4"/>
       <c r="I727" s="3"/>
       <c r="J727" s="1"/>
     </row>
-    <row r="728" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B728" s="4"/>
       <c r="I728" s="3"/>
       <c r="J728" s="1"/>
     </row>
-    <row r="729" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B729" s="4"/>
       <c r="I729" s="3"/>
       <c r="J729" s="1"/>
     </row>
-    <row r="730" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B730" s="4"/>
       <c r="I730" s="3"/>
       <c r="J730" s="1"/>
     </row>
-    <row r="731" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B731" s="4"/>
       <c r="I731" s="3"/>
       <c r="J731" s="1"/>
     </row>
-    <row r="732" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B732" s="4"/>
       <c r="I732" s="3"/>
       <c r="J732" s="1"/>
     </row>
-    <row r="733" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B733" s="4"/>
       <c r="I733" s="3"/>
       <c r="J733" s="1"/>
     </row>
-    <row r="734" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B734" s="4"/>
       <c r="I734" s="3"/>
       <c r="J734" s="1"/>
     </row>
-    <row r="735" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A735" t="s">
+        <v>0</v>
+      </c>
       <c r="B735" s="4"/>
       <c r="I735" s="3"/>
       <c r="J735" s="1"/>
     </row>
-    <row r="736" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B736" s="4"/>
       <c r="I736" s="3"/>
       <c r="J736" s="1"/>
     </row>
-    <row r="737" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A737" t="s">
-        <v>0</v>
-      </c>
+    <row r="737" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B737" s="4"/>
       <c r="I737" s="3"/>
       <c r="J737" s="1"/>
     </row>
-    <row r="738" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="738" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B738" s="4"/>
       <c r="I738" s="3"/>
       <c r="J738" s="1"/>
     </row>
-    <row r="739" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="739" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B739" s="4"/>
       <c r="I739" s="3"/>
       <c r="J739" s="1"/>
     </row>
-    <row r="740" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="740" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B740" s="4"/>
       <c r="I740" s="3"/>
       <c r="J740" s="1"/>
     </row>
-    <row r="741" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="741" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B741" s="4"/>
       <c r="I741" s="3"/>
       <c r="J741" s="1"/>
     </row>
-    <row r="742" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="742" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B742" s="4"/>
       <c r="I742" s="3"/>
       <c r="J742" s="1"/>
     </row>
-    <row r="743" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="743" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B743" s="4"/>
       <c r="I743" s="3"/>
       <c r="J743" s="1"/>
     </row>
-    <row r="744" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="744" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B744" s="4"/>
       <c r="I744" s="3"/>
       <c r="J744" s="1"/>
     </row>
-    <row r="745" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="745" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B745" s="4"/>
       <c r="I745" s="3"/>
       <c r="J745" s="1"/>
     </row>
-    <row r="746" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="746" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B746" s="4"/>
       <c r="I746" s="3"/>
       <c r="J746" s="1"/>
     </row>
-    <row r="747" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="747" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B747" s="4"/>
       <c r="I747" s="3"/>
       <c r="J747" s="1"/>
     </row>
-    <row r="748" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="748" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B748" s="4"/>
       <c r="I748" s="3"/>
       <c r="J748" s="1"/>
     </row>
-    <row r="749" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="749" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B749" s="4"/>
       <c r="I749" s="3"/>
       <c r="J749" s="1"/>
     </row>
-    <row r="750" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="750" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B750" s="4"/>
       <c r="I750" s="3"/>
       <c r="J750" s="1"/>
     </row>
-    <row r="751" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="751" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B751" s="4"/>
       <c r="I751" s="3"/>
       <c r="J751" s="1"/>
     </row>
-    <row r="752" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="752" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B752" s="4"/>
       <c r="I752" s="3"/>
       <c r="J752" s="1"/>
     </row>
     <row r="753" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A753" t="s">
+        <v>0</v>
+      </c>
       <c r="B753" s="4"/>
       <c r="I753" s="3"/>
       <c r="J753" s="1"/>
@@ -32172,9 +32517,6 @@
       <c r="J754" s="1"/>
     </row>
     <row r="755" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A755" t="s">
-        <v>0</v>
-      </c>
       <c r="B755" s="4"/>
       <c r="I755" s="3"/>
       <c r="J755" s="1"/>
@@ -32345,7 +32687,6 @@
       <c r="J788" s="1"/>
     </row>
     <row r="789" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B789" s="4"/>
       <c r="I789" s="3"/>
       <c r="J789" s="1"/>
     </row>
@@ -32355,6 +32696,7 @@
       <c r="J790" s="1"/>
     </row>
     <row r="791" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B791" s="4"/>
       <c r="I791" s="3"/>
       <c r="J791" s="1"/>
     </row>
@@ -32405,6 +32747,7 @@
     </row>
     <row r="801" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B801" s="4"/>
+      <c r="G801" s="4"/>
       <c r="I801" s="3"/>
       <c r="J801" s="1"/>
     </row>
@@ -32415,7 +32758,6 @@
     </row>
     <row r="803" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B803" s="4"/>
-      <c r="G803" s="4"/>
       <c r="I803" s="3"/>
       <c r="J803" s="1"/>
     </row>
@@ -32543,16 +32885,6 @@
       <c r="B828" s="4"/>
       <c r="I828" s="3"/>
       <c r="J828" s="1"/>
-    </row>
-    <row r="829" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B829" s="4"/>
-      <c r="I829" s="3"/>
-      <c r="J829" s="1"/>
-    </row>
-    <row r="830" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B830" s="4"/>
-      <c r="I830" s="3"/>
-      <c r="J830" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\5_MB MMA\09_Information\10_FTQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234EDC18-20D9-4775-80C6-E7B7E0CD7EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF7D32A-A3F0-450F-B0E3-DFE2ACE66B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$66</definedName>
     <definedName name="DATA_01">[1]Data_Lineal!$H$4:$Y$30</definedName>
     <definedName name="DB_01">#REF!</definedName>
     <definedName name="DB_CAP01">'[2]CAPACIDAD (1)'!$X$9:$AM$29</definedName>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="58">
   <si>
     <t>*</t>
   </si>
@@ -239,18 +239,6 @@
   <si>
     <t>Falla 3121.022 Op.EOL</t>
   </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Safe launch</t>
-  </si>
-  <si>
-    <t>Palanca rayada</t>
-  </si>
-  <si>
-    <t>Pines desalineados</t>
-  </si>
 </sst>
 </file>
 
@@ -331,7 +319,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -363,25 +351,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -24367,7 +24342,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K67" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K66" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CDAA4D20-2955-41E2-BD7E-9330E166FFF4}" name="Fecha" dataDxfId="18"/>
     <tableColumn id="9" xr3:uid="{F70BB124-92DE-4024-874C-EE3BA966CDE6}" name="Semana" dataDxfId="17">
@@ -24393,7 +24368,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S68" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S66" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D688BA2E-A64E-4433-85E0-7EDBF854AF60}" name="Fecha" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{D3EA5E8D-DD68-48AC-8DAC-4A4077839479}" name="Semana" dataDxfId="5">
@@ -24695,46 +24670,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
       <c r="K1" s="6"/>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
     </row>
     <row r="2" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
       <c r="K2" s="6"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.3">
       <c r="G3" s="1">
@@ -28393,94 +28368,22 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="2:19" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="12">
-        <v>46254</v>
-      </c>
-      <c r="C67" s="13">
-        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>34</v>
-      </c>
-      <c r="D67" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E67" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F67" s="14">
-        <v>10532587</v>
-      </c>
-      <c r="G67" s="13">
-        <v>200</v>
-      </c>
-      <c r="H67" s="13">
-        <v>2</v>
-      </c>
-      <c r="I67" s="15">
-        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.01</v>
-      </c>
-      <c r="J67" s="13">
-        <f>ABS(G$3-I67)</f>
-        <v>0.99</v>
-      </c>
-      <c r="K67" s="16">
-        <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.99</v>
-      </c>
-      <c r="M67" s="12">
-        <v>46254</v>
-      </c>
-      <c r="N67" s="13">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>34</v>
-      </c>
-      <c r="O67" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="P67" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q67" s="14">
-        <v>10532587</v>
-      </c>
-      <c r="R67" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="S67" s="13">
-        <v>1</v>
-      </c>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B67" s="4"/>
+      <c r="F67" s="9"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="11"/>
+      <c r="M67" s="4"/>
+      <c r="Q67" s="9"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B68" s="4"/>
-      <c r="G68" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="I68" s="3"/>
       <c r="J68" s="1"/>
       <c r="K68" s="5"/>
-      <c r="M68" s="4">
-        <v>46254</v>
-      </c>
-      <c r="N68" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>34</v>
-      </c>
-      <c r="O68" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P68" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q68" s="9">
-        <v>10532587</v>
-      </c>
-      <c r="R68" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="S68" s="1">
-        <v>1</v>
-      </c>
+      <c r="M68" s="4"/>
+      <c r="Q68" s="9"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B69" s="4"/>

--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\5_MB MMA\09_Information\10_FTQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF7D32A-A3F0-450F-B0E3-DFE2ACE66B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F42B67-C91F-44E4-9B5D-7FC6FAA5A1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE DE DATOS" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$67</definedName>
     <definedName name="DATA_01">[1]Data_Lineal!$H$4:$Y$30</definedName>
     <definedName name="DB_01">#REF!</definedName>
     <definedName name="DB_CAP01">'[2]CAPACIDAD (1)'!$X$9:$AM$29</definedName>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="61">
   <si>
     <t>*</t>
   </si>
@@ -239,6 +239,15 @@
   <si>
     <t>Falla 3121.022 Op.EOL</t>
   </si>
+  <si>
+    <t>Safe launch</t>
+  </si>
+  <si>
+    <t>Palanca Rayada</t>
+  </si>
+  <si>
+    <t>Pines desalineados</t>
+  </si>
 </sst>
 </file>
 
@@ -319,7 +328,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -356,6 +365,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -24342,7 +24354,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K66" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K67" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CDAA4D20-2955-41E2-BD7E-9330E166FFF4}" name="Fecha" dataDxfId="18"/>
     <tableColumn id="9" xr3:uid="{F70BB124-92DE-4024-874C-EE3BA966CDE6}" name="Semana" dataDxfId="17">
@@ -24368,7 +24380,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S66" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S68" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D688BA2E-A64E-4433-85E0-7EDBF854AF60}" name="Fecha" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{D3EA5E8D-DD68-48AC-8DAC-4A4077839479}" name="Semana" dataDxfId="5">
@@ -28369,21 +28381,90 @@
       </c>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B67" s="4"/>
-      <c r="F67" s="9"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="11"/>
-      <c r="M67" s="4"/>
-      <c r="Q67" s="9"/>
+      <c r="B67" s="4">
+        <v>46255</v>
+      </c>
+      <c r="C67" s="13">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>34</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F67" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="G67" s="1">
+        <v>200</v>
+      </c>
+      <c r="H67" s="1">
+        <v>2</v>
+      </c>
+      <c r="I67" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="J67" s="13">
+        <f>ABS(G$3-I67)</f>
+        <v>0.99</v>
+      </c>
+      <c r="K67" s="11">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.99</v>
+      </c>
+      <c r="M67" s="4">
+        <v>46254</v>
+      </c>
+      <c r="N67" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>34</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P67" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="S67" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B68" s="4"/>
       <c r="I68" s="3"/>
       <c r="J68" s="1"/>
       <c r="K68" s="5"/>
-      <c r="M68" s="4"/>
-      <c r="Q68" s="9"/>
+      <c r="M68" s="4">
+        <v>46254</v>
+      </c>
+      <c r="N68" s="13">
+        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>34</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P68" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q68" s="9">
+        <v>12289475</v>
+      </c>
+      <c r="R68" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="S68" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B69" s="4"/>
@@ -28391,6 +28472,8 @@
       <c r="J69" s="1"/>
       <c r="K69" s="5"/>
       <c r="M69" s="4"/>
+      <c r="N69" s="13"/>
+      <c r="Q69" s="9"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B70" s="4"/>

--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\5_MB MMA\09_Information\10_FTQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F42B67-C91F-44E4-9B5D-7FC6FAA5A1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB48A97B-972B-445A-87C5-02BE51DEDE70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE DE DATOS" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$66</definedName>
     <definedName name="DATA_01">[1]Data_Lineal!$H$4:$Y$30</definedName>
     <definedName name="DB_01">#REF!</definedName>
     <definedName name="DB_CAP01">'[2]CAPACIDAD (1)'!$X$9:$AM$29</definedName>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="58">
   <si>
     <t>*</t>
   </si>
@@ -239,15 +239,6 @@
   <si>
     <t>Falla 3121.022 Op.EOL</t>
   </si>
-  <si>
-    <t>Safe launch</t>
-  </si>
-  <si>
-    <t>Palanca Rayada</t>
-  </si>
-  <si>
-    <t>Pines desalineados</t>
-  </si>
 </sst>
 </file>
 
@@ -328,7 +319,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -365,9 +356,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -24354,7 +24342,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K67" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K66" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CDAA4D20-2955-41E2-BD7E-9330E166FFF4}" name="Fecha" dataDxfId="18"/>
     <tableColumn id="9" xr3:uid="{F70BB124-92DE-4024-874C-EE3BA966CDE6}" name="Semana" dataDxfId="17">
@@ -24380,7 +24368,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S68" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S66" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D688BA2E-A64E-4433-85E0-7EDBF854AF60}" name="Fecha" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{D3EA5E8D-DD68-48AC-8DAC-4A4077839479}" name="Semana" dataDxfId="5">
@@ -24659,6 +24647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A1B645-8848-474A-88BA-FA9209B01B4F}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:V828"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -28381,90 +28370,21 @@
       </c>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B67" s="4">
-        <v>46255</v>
-      </c>
-      <c r="C67" s="13">
-        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>34</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F67" s="9">
-        <v>12289475</v>
-      </c>
-      <c r="G67" s="1">
-        <v>200</v>
-      </c>
-      <c r="H67" s="1">
-        <v>2</v>
-      </c>
-      <c r="I67" s="3">
-        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.01</v>
-      </c>
-      <c r="J67" s="13">
-        <f>ABS(G$3-I67)</f>
-        <v>0.99</v>
-      </c>
-      <c r="K67" s="11">
-        <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.99</v>
-      </c>
-      <c r="M67" s="4">
-        <v>46254</v>
-      </c>
-      <c r="N67" s="13">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>34</v>
-      </c>
-      <c r="O67" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P67" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q67" s="9">
-        <v>12289475</v>
-      </c>
-      <c r="R67" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="S67" s="1">
-        <v>1</v>
-      </c>
+      <c r="B67" s="4"/>
+      <c r="F67" s="9"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="11"/>
+      <c r="M67" s="4"/>
+      <c r="Q67" s="9"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B68" s="4"/>
       <c r="I68" s="3"/>
       <c r="J68" s="1"/>
       <c r="K68" s="5"/>
-      <c r="M68" s="4">
-        <v>46254</v>
-      </c>
-      <c r="N68" s="13">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>34</v>
-      </c>
-      <c r="O68" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P68" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q68" s="9">
-        <v>12289475</v>
-      </c>
-      <c r="R68" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="S68" s="1">
-        <v>1</v>
-      </c>
+      <c r="M68" s="4"/>
+      <c r="Q68" s="9"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B69" s="4"/>
@@ -28472,7 +28392,6 @@
       <c r="J69" s="1"/>
       <c r="K69" s="5"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="13"/>
       <c r="Q69" s="9"/>
     </row>
     <row r="70" spans="2:19" x14ac:dyDescent="0.3">
